--- a/data/historico/semana_323.xlsx
+++ b/data/historico/semana_323.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 20min'!$A$2:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$41</definedName>
@@ -1520,25 +1520,25 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>23.67</v>
+        <v>22.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>5.63</v>
+        <v>5.52</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>5</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>11.27</v>
+        <v>11.11</v>
       </c>
       <c r="K8" s="5" t="n">
         <v>0</v>
@@ -1562,49 +1562,49 @@
         <v>0</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="U8" s="5" t="n">
-        <v>36.04</v>
+        <v>31.3</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>4.71</v>
+        <v>5.26</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>14.12</v>
+        <v>21.03</v>
       </c>
       <c r="X8" s="5" t="n">
-        <v>2.22</v>
+        <v>2.07</v>
       </c>
       <c r="Y8" s="5" t="inlineStr">
         <is>
-          <t>R$ 99,47</t>
+          <t>R$ 106,74</t>
         </is>
       </c>
       <c r="Z8" s="5" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA8" s="5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AB8" s="5" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC8" s="5" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:33</t>
         </is>
       </c>
     </row>
@@ -1940,25 +1940,25 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>33</v>
+        <v>24.75</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>4.05</v>
+        <v>4.36</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>4</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>16.67</v>
+        <v>13.13</v>
       </c>
       <c r="K12" s="5" t="n">
         <v>0</v>
@@ -1967,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" s="5" t="n">
         <v>0</v>
@@ -1982,49 +1982,49 @@
         <v>0</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="S12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="U12" s="5" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="V12" s="5" t="n">
-        <v>5.82</v>
+        <v>3.68</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>11.65</v>
+        <v>14.7</v>
       </c>
       <c r="X12" s="5" t="n">
-        <v>2.22</v>
+        <v>1.8</v>
       </c>
       <c r="Y12" s="5" t="inlineStr">
         <is>
-          <t>R$ 99,35</t>
+          <t>R$ 122,80</t>
         </is>
       </c>
       <c r="Z12" s="5" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA12" s="5" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AB12" s="5" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC12" s="5" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:49</t>
         </is>
       </c>
     </row>
@@ -2465,16 +2465,16 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>31.67</v>
+        <v>33</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>9.220000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="H17" s="4" t="n">
         <v>9</v>
@@ -2492,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -2513,43 +2513,43 @@
         <v>0</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>11.21</v>
+        <v>8.33</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>6.74</v>
+        <v>6.87</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>20.22</v>
+        <v>27.48</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>4.87</v>
+        <v>5.04</v>
       </c>
       <c r="Y17" s="4" t="inlineStr">
         <is>
-          <t>R$ 45,42</t>
+          <t>R$ 43,88</t>
         </is>
       </c>
       <c r="Z17" s="4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA17" s="4" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AB17" s="4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC17" s="4" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>16:52</t>
         </is>
       </c>
     </row>
@@ -3612,16 +3612,16 @@
         </is>
       </c>
       <c r="D28" s="4" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E28" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>18.25</v>
+        <v>21</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>5</v>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -3654,29 +3654,29 @@
         <v>0</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="S28" s="4" t="n">
         <v>1</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>48.23</v>
+        <v>46.5</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>3.14</v>
+        <v>3.98</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>12.57</v>
+        <v>15.93</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.74</v>
+        <v>1.98</v>
       </c>
       <c r="Y28" s="4" t="inlineStr">
         <is>
-          <t>R$ 127,22</t>
+          <t>R$ 111,45</t>
         </is>
       </c>
       <c r="Z28" s="4" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="AB28" s="4" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC28" s="4" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:58</t>
         </is>
       </c>
     </row>
@@ -5541,19 +5541,19 @@
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>36.04</v>
+        <v>31.3</v>
       </c>
       <c r="H8" s="2" t="n"/>
       <c r="I8" s="2" t="n"/>
@@ -5657,19 +5657,19 @@
         </is>
       </c>
       <c r="C12" s="25" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="D12" s="25" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E12" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="25" t="n">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="H12" s="2" t="n"/>
       <c r="I12" s="2" t="n"/>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="C17" s="25" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="D17" s="25" t="n">
         <v>12</v>
@@ -5811,10 +5811,10 @@
         <v>0</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>11.21</v>
+        <v>8.33</v>
       </c>
       <c r="H17" s="2" t="n"/>
       <c r="I17" s="2" t="n"/>
@@ -6121,19 +6121,19 @@
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D28" s="25" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E28" s="25" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="25" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>48.23</v>
+        <v>46.5</v>
       </c>
       <c r="H28" s="2" t="n"/>
       <c r="I28" s="2" t="n"/>
@@ -6527,19 +6527,19 @@
         </is>
       </c>
       <c r="C42" s="37" t="n">
-        <v>3346</v>
+        <v>3446</v>
       </c>
       <c r="D42" s="37" t="n">
-        <v>1288</v>
+        <v>1303</v>
       </c>
       <c r="E42" s="37" t="n">
         <v>6</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>4640</v>
+        <v>4755</v>
       </c>
       <c r="G42" s="37" t="n">
-        <v>27.89</v>
+        <v>27.53</v>
       </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
@@ -7188,19 +7188,19 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>12.5</v>
+        <v>12.36</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>0</v>
@@ -7234,22 +7234,22 @@
       <c r="V3" s="4" t="inlineStr"/>
       <c r="W3" s="4" t="inlineStr"/>
       <c r="X3" s="4" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="Y3" s="4" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="Z3" s="4" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AA3" s="4" t="inlineStr">
         <is>
-          <t>R$ 212,20</t>
+          <t>R$ 195,04</t>
         </is>
       </c>
       <c r="AB3" s="4" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AC3" s="4" t="inlineStr">
@@ -7389,7 +7389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7697,13 +7697,13 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>100</v>
@@ -8023,10 +8023,10 @@
         <v>8</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>94.3</v>
+        <v>98.2</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
@@ -8131,34 +8131,34 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="5" t="n">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
+      <c r="F24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
         </is>
       </c>
     </row>
@@ -8168,25 +8168,25 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>88</v>
+        <v>89.8</v>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
@@ -8200,12 +8200,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -8215,10 +8215,10 @@
         <v>8</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -8232,25 +8232,25 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>87.2</v>
+        <v>87.7</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -8282,7 +8282,7 @@
         <v>3</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>86.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -8296,12 +8296,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -8311,10 +8311,10 @@
         <v>8</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>86.5</v>
+        <v>87.2</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
@@ -8328,25 +8328,25 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>85.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
@@ -8360,25 +8360,25 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>83.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         </is>
       </c>
       <c r="D121" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" s="46" t="n">
         <v>0.5</v>
@@ -11211,7 +11211,7 @@
         <v>0.5</v>
       </c>
       <c r="H121" s="46" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="122">
@@ -11227,11 +11227,11 @@
       </c>
       <c r="C122" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D122" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" s="46" t="n">
         <v>0.3</v>
@@ -11243,7 +11243,7 @@
         <v>0.6</v>
       </c>
       <c r="H122" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="123">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="C123" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D123" s="46" t="n">
@@ -11291,23 +11291,23 @@
       </c>
       <c r="C124" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D124" s="46" t="n">
         <v>3</v>
       </c>
       <c r="E124" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F124" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G124" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H124" s="46" t="n">
-        <v>-9</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="125">
@@ -11323,55 +11323,55 @@
       </c>
       <c r="C125" s="46" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D125" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F125" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G125" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H125" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="46" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B126" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C126" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D125" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="E125" s="46" t="n">
+      <c r="D126" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E126" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F125" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G125" s="46" t="n">
+      <c r="F126" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G126" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H125" s="46" t="n">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="45" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-      <c r="B126" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C126" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D126" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F126" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H126" s="45" t="n">
-        <v>5</v>
+      <c r="H126" s="46" t="n">
+        <v>-4</v>
       </c>
     </row>
     <row r="127">
@@ -11387,55 +11387,55 @@
       </c>
       <c r="C127" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D127" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F127" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H127" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="45" t="inlineStr">
+        <is>
+          <t>Fabiana de Figueredo Vieira</t>
+        </is>
+      </c>
+      <c r="B128" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C128" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D127" s="45" t="n">
+      <c r="D128" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E127" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F127" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H127" s="45" t="n">
+      <c r="E128" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" s="45" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="46" t="inlineStr">
-        <is>
-          <t>Fabiana de Figueredo Vieira</t>
-        </is>
-      </c>
-      <c r="B128" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C128" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D128" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F128" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H128" s="46" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="129">
@@ -11451,23 +11451,23 @@
       </c>
       <c r="C129" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D129" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E129" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F129" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G129" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H129" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="130">
@@ -11483,11 +11483,11 @@
       </c>
       <c r="C130" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D130" s="46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E130" s="46" t="n">
         <v>0.3</v>
@@ -11499,7 +11499,7 @@
         <v>0.6</v>
       </c>
       <c r="H130" s="46" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="131">
@@ -11515,55 +11515,55 @@
       </c>
       <c r="C131" s="46" t="inlineStr">
         <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D131" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F131" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H131" s="46" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="46" t="inlineStr">
+        <is>
+          <t>Fabiana de Figueredo Vieira</t>
+        </is>
+      </c>
+      <c r="B132" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C132" s="46" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D131" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" s="46" t="n">
+      <c r="D132" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="F131" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G131" s="46" t="n">
+      <c r="F132" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G132" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="H131" s="46" t="n">
+      <c r="H132" s="46" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="45" t="inlineStr">
-        <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
-        </is>
-      </c>
-      <c r="B132" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C132" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D132" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F132" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H132" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="133">
@@ -11579,55 +11579,55 @@
       </c>
       <c r="C133" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D133" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F133" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H133" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="45" t="inlineStr">
+        <is>
+          <t>Gabriel Alan de Oliveira Martins</t>
+        </is>
+      </c>
+      <c r="B134" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C134" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D133" s="45" t="n">
+      <c r="D134" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E133" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F133" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H133" s="45" t="n">
+      <c r="E134" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" s="45" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="46" t="inlineStr">
-        <is>
-          <t>Gabriel Alan de Oliveira Martins</t>
-        </is>
-      </c>
-      <c r="B134" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C134" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D134" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F134" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H134" s="46" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="135">
@@ -11643,23 +11643,23 @@
       </c>
       <c r="C135" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D135" s="46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E135" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F135" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G135" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H135" s="46" t="n">
-        <v>-2.4</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="136">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="C136" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D136" s="46" t="n">
@@ -11707,55 +11707,55 @@
       </c>
       <c r="C137" s="46" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D137" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E137" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F137" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G137" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H137" s="46" t="n">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="46" t="inlineStr">
+        <is>
+          <t>Gabriel Alan de Oliveira Martins</t>
+        </is>
+      </c>
+      <c r="B138" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C138" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D137" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E137" s="46" t="n">
+      <c r="D138" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E138" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F137" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G137" s="46" t="n">
+      <c r="F138" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G138" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H137" s="46" t="n">
+      <c r="H138" s="46" t="n">
         <v>-0.8</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="45" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-      <c r="B138" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C138" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D138" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F138" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H138" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="139">
@@ -11771,55 +11771,55 @@
       </c>
       <c r="C139" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D139" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F139" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H139" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="45" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B140" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C140" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D139" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E139" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F139" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H139" s="45" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="46" t="inlineStr">
-        <is>
-          <t>Geancarlos Ferreira Barrios</t>
-        </is>
-      </c>
-      <c r="B140" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C140" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D140" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E140" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F140" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H140" s="46" t="n">
-        <v>-1</v>
+      <c r="D140" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="141">
@@ -11835,23 +11835,23 @@
       </c>
       <c r="C141" s="46" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D141" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F141" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G141" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H141" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="142">
@@ -11867,11 +11867,11 @@
       </c>
       <c r="C142" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D142" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E142" s="46" t="n">
         <v>0.3</v>
@@ -11883,7 +11883,7 @@
         <v>0.6</v>
       </c>
       <c r="H142" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="143">
@@ -11899,11 +11899,11 @@
       </c>
       <c r="C143" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D143" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" s="46" t="n">
         <v>0.3</v>
@@ -11915,7 +11915,7 @@
         <v>0.6</v>
       </c>
       <c r="H143" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="144">
@@ -11931,11 +11931,11 @@
       </c>
       <c r="C144" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D144" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E144" s="46" t="n">
         <v>0.3</v>
@@ -11947,7 +11947,7 @@
         <v>0.6</v>
       </c>
       <c r="H144" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="145">
@@ -11963,55 +11963,55 @@
       </c>
       <c r="C145" s="46" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D145" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E145" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F145" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G145" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H145" s="46" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="46" t="inlineStr">
+        <is>
+          <t>Geancarlos Ferreira Barrios</t>
+        </is>
+      </c>
+      <c r="B146" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C146" s="46" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D145" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" s="46" t="n">
+      <c r="D146" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="F145" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G145" s="46" t="n">
+      <c r="F146" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G146" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="H145" s="46" t="n">
+      <c r="H146" s="46" t="n">
         <v>-3</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="45" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="B146" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C146" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D146" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E146" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F146" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H146" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="147">
@@ -12027,119 +12027,119 @@
       </c>
       <c r="C147" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D147" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F147" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H147" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="45" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="B148" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C148" s="45" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D148" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F148" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H148" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="45" t="inlineStr">
+        <is>
+          <t>Gilmar Bitencourt Luiz</t>
+        </is>
+      </c>
+      <c r="B149" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C149" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D147" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E147" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" s="45" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="46" t="inlineStr">
+      <c r="D149" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E149" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="45" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="46" t="inlineStr">
         <is>
           <t>Gilmar Bitencourt Luiz</t>
         </is>
       </c>
-      <c r="B148" s="46" t="inlineStr">
+      <c r="B150" s="46" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C148" s="46" t="inlineStr">
+      <c r="C150" s="46" t="inlineStr">
         <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D148" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" s="46" t="n">
+      <c r="D150" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" s="46" t="n">
         <v>0.3</v>
       </c>
-      <c r="F148" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G148" s="46" t="n">
+      <c r="F150" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" s="46" t="n">
         <v>0.6</v>
       </c>
-      <c r="H148" s="46" t="n">
+      <c r="H150" s="46" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="46" t="inlineStr">
-        <is>
-          <t>Gilmar Bitencourt Luiz</t>
-        </is>
-      </c>
-      <c r="B149" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C149" s="46" t="inlineStr">
-        <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
-        </is>
-      </c>
-      <c r="D149" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E149" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F149" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G149" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="H149" s="46" t="n">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="45" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B150" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C150" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D150" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F150" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H150" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="151">
@@ -12155,55 +12155,55 @@
       </c>
       <c r="C151" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D151" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F151" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H151" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="45" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B152" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C152" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D151" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E151" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" s="45" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="46" t="inlineStr">
-        <is>
-          <t>Gisele Lopes Justiniano</t>
-        </is>
-      </c>
-      <c r="B152" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C152" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D152" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E152" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F152" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H152" s="46" t="n">
-        <v>-1</v>
+      <c r="D152" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -12219,23 +12219,23 @@
       </c>
       <c r="C153" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D153" s="46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E153" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F153" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G153" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H153" s="46" t="n">
-        <v>-2.4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="154">
@@ -12251,11 +12251,11 @@
       </c>
       <c r="C154" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D154" s="46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E154" s="46" t="n">
         <v>0.3</v>
@@ -12267,7 +12267,7 @@
         <v>0.6</v>
       </c>
       <c r="H154" s="46" t="n">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="155">
@@ -12283,11 +12283,11 @@
       </c>
       <c r="C155" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D155" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" s="46" t="n">
         <v>0.3</v>
@@ -12299,7 +12299,7 @@
         <v>0.6</v>
       </c>
       <c r="H155" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="156">
@@ -12315,87 +12315,87 @@
       </c>
       <c r="C156" s="46" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D156" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F156" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H156" s="46" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="46" t="inlineStr">
+        <is>
+          <t>Gisele Lopes Justiniano</t>
+        </is>
+      </c>
+      <c r="B157" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C157" s="46" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D156" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" s="46" t="n">
+      <c r="D157" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="F156" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" s="46" t="n">
+      <c r="F157" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="H156" s="46" t="n">
+      <c r="H157" s="46" t="n">
         <v>-3</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="45" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="45" t="inlineStr">
         <is>
           <t>Gisele Olimpia Torres</t>
         </is>
       </c>
-      <c r="B157" s="45" t="inlineStr">
+      <c r="B158" s="45" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C157" s="45" t="inlineStr">
+      <c r="C158" s="45" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D157" s="45" t="n">
+      <c r="D158" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E157" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F157" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" s="45" t="n">
+      <c r="E158" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" s="45" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="46" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="B158" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C158" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D158" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F158" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H158" s="46" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="159">
@@ -12411,23 +12411,23 @@
       </c>
       <c r="C159" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D159" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E159" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F159" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G159" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H159" s="46" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="160">
@@ -12443,11 +12443,11 @@
       </c>
       <c r="C160" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D160" s="46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E160" s="46" t="n">
         <v>0.3</v>
@@ -12459,7 +12459,7 @@
         <v>0.6</v>
       </c>
       <c r="H160" s="46" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="161">
@@ -12475,11 +12475,11 @@
       </c>
       <c r="C161" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D161" s="46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E161" s="46" t="n">
         <v>0.3</v>
@@ -12491,7 +12491,7 @@
         <v>0.6</v>
       </c>
       <c r="H161" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="162">
@@ -12507,23 +12507,23 @@
       </c>
       <c r="C162" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D162" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E162" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F162" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G162" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H162" s="46" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="163">
@@ -12539,55 +12539,55 @@
       </c>
       <c r="C163" s="46" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D163" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F163" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H163" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="46" t="inlineStr">
+        <is>
+          <t>Gisele Olimpia Torres</t>
+        </is>
+      </c>
+      <c r="B164" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C164" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D163" s="46" t="n">
+      <c r="D164" s="46" t="n">
         <v>55</v>
       </c>
-      <c r="E163" s="46" t="n">
+      <c r="E164" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F163" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G163" s="46" t="n">
+      <c r="F164" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G164" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H163" s="46" t="n">
+      <c r="H164" s="46" t="n">
         <v>-22</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="45" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="B164" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C164" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D164" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E164" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F164" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H164" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="165">
@@ -12603,55 +12603,55 @@
       </c>
       <c r="C165" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D165" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F165" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H165" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="45" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="B166" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C166" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D165" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E165" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F165" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H165" s="45" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="46" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="B166" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C166" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D166" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E166" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F166" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G166" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H166" s="46" t="n">
-        <v>-1.2</v>
+      <c r="D166" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="C167" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D167" s="46" t="n">
@@ -12699,87 +12699,87 @@
       </c>
       <c r="C168" s="46" t="inlineStr">
         <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D168" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F168" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H168" s="46" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="46" t="inlineStr">
+        <is>
+          <t>Juliana Patricia Goncalves</t>
+        </is>
+      </c>
+      <c r="B169" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C169" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D168" s="46" t="n">
+      <c r="D169" s="46" t="n">
         <v>37</v>
       </c>
-      <c r="E168" s="46" t="n">
+      <c r="E169" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F168" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G168" s="46" t="n">
+      <c r="F169" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H168" s="46" t="n">
+      <c r="H169" s="46" t="n">
         <v>-14.8</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="45" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="45" t="inlineStr">
         <is>
           <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
-      <c r="B169" s="45" t="inlineStr">
+      <c r="B170" s="45" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C169" s="45" t="inlineStr">
+      <c r="C170" s="45" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D169" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E169" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F169" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G169" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H169" s="45" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="46" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="B170" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C170" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D170" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E170" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F170" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G170" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H170" s="46" t="n">
-        <v>-0.6</v>
+      <c r="D170" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="171">
@@ -12795,11 +12795,11 @@
       </c>
       <c r="C171" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D171" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E171" s="46" t="n">
         <v>0.3</v>
@@ -12811,7 +12811,7 @@
         <v>0.6</v>
       </c>
       <c r="H171" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="172">
@@ -12827,23 +12827,23 @@
       </c>
       <c r="C172" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D172" s="46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E172" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F172" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G172" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H172" s="46" t="n">
-        <v>-12</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="173">
@@ -12859,29 +12859,29 @@
       </c>
       <c r="C173" s="46" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D173" s="46" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="E173" s="46" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="F173" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G173" s="46" t="n">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="H173" s="46" t="n">
-        <v>-15.6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="46" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="B174" s="46" t="inlineStr">
@@ -12891,23 +12891,23 @@
       </c>
       <c r="C174" s="46" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Visita rápida</t>
         </is>
       </c>
       <c r="D174" s="46" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="E174" s="46" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="F174" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G174" s="46" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H174" s="46" t="n">
-        <v>-2</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="175">
@@ -12923,23 +12923,23 @@
       </c>
       <c r="C175" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D175" s="46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E175" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F175" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G175" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H175" s="46" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="176">
@@ -12955,11 +12955,11 @@
       </c>
       <c r="C176" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D176" s="46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E176" s="46" t="n">
         <v>0.3</v>
@@ -12971,7 +12971,7 @@
         <v>0.6</v>
       </c>
       <c r="H176" s="46" t="n">
-        <v>-1.2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="177">
@@ -12987,11 +12987,11 @@
       </c>
       <c r="C177" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D177" s="46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E177" s="46" t="n">
         <v>0.3</v>
@@ -13003,7 +13003,7 @@
         <v>0.6</v>
       </c>
       <c r="H177" s="46" t="n">
-        <v>-2.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="178">
@@ -13019,23 +13019,23 @@
       </c>
       <c r="C178" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D178" s="46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E178" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F178" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G178" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H178" s="46" t="n">
-        <v>-6</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="179">
@@ -13051,23 +13051,23 @@
       </c>
       <c r="C179" s="46" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D179" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F179" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E179" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F179" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G179" s="46" t="n">
-        <v>1</v>
-      </c>
       <c r="H179" s="46" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="180">
@@ -13083,55 +13083,55 @@
       </c>
       <c r="C180" s="46" t="inlineStr">
         <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D180" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E180" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F180" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="46" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="B181" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C181" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D180" s="46" t="n">
+      <c r="D181" s="46" t="n">
         <v>20</v>
       </c>
-      <c r="E180" s="46" t="n">
+      <c r="E181" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F180" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G180" s="46" t="n">
+      <c r="F181" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H180" s="46" t="n">
+      <c r="H181" s="46" t="n">
         <v>-8</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="45" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="B181" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C181" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D181" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F181" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H181" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="182">
@@ -13147,55 +13147,55 @@
       </c>
       <c r="C182" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D182" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F182" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H182" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="45" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="B183" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C183" s="45" t="inlineStr">
+        <is>
           <t>Bônus: pontualidade perfeita no período</t>
         </is>
       </c>
-      <c r="D182" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E182" s="45" t="n">
+      <c r="D183" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="F182" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G182" s="45" t="n">
+      <c r="F183" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="H182" s="45" t="n">
+      <c r="H183" s="45" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="46" t="inlineStr">
-        <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
-        </is>
-      </c>
-      <c r="B183" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C183" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D183" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F183" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H183" s="46" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="184">
@@ -13211,87 +13211,87 @@
       </c>
       <c r="C184" s="46" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D184" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F184" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H184" s="46" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="46" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="B185" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C185" s="46" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D184" s="46" t="n">
+      <c r="D185" s="46" t="n">
         <v>7</v>
       </c>
-      <c r="E184" s="46" t="n">
+      <c r="E185" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="F184" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G184" s="46" t="n">
+      <c r="F185" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="H184" s="46" t="n">
+      <c r="H185" s="46" t="n">
         <v>-21</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="45" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="45" t="inlineStr">
         <is>
           <t>Mateus Falcao de Souza</t>
         </is>
       </c>
-      <c r="B185" s="45" t="inlineStr">
+      <c r="B186" s="45" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C185" s="45" t="inlineStr">
+      <c r="C186" s="45" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D185" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E185" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F185" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G185" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H185" s="45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="46" t="inlineStr">
-        <is>
-          <t>Mateus Falcao de Souza</t>
-        </is>
-      </c>
-      <c r="B186" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C186" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D186" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E186" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F186" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G186" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H186" s="46" t="n">
-        <v>-1.5</v>
+      <c r="D186" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" s="45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="187">
@@ -13307,23 +13307,23 @@
       </c>
       <c r="C187" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D187" s="46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E187" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F187" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G187" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H187" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="188">
@@ -13339,11 +13339,11 @@
       </c>
       <c r="C188" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D188" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E188" s="46" t="n">
         <v>0.3</v>
@@ -13355,7 +13355,7 @@
         <v>0.6</v>
       </c>
       <c r="H188" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="189">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C189" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D189" s="46" t="n">
@@ -13403,23 +13403,23 @@
       </c>
       <c r="C190" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D190" s="46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E190" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F190" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G190" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H190" s="46" t="n">
-        <v>-9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="191">
@@ -13435,55 +13435,55 @@
       </c>
       <c r="C191" s="46" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D191" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E191" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F191" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H191" s="46" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="46" t="inlineStr">
+        <is>
+          <t>Mateus Falcao de Souza</t>
+        </is>
+      </c>
+      <c r="B192" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C192" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D191" s="46" t="n">
+      <c r="D192" s="46" t="n">
         <v>16</v>
       </c>
-      <c r="E191" s="46" t="n">
+      <c r="E192" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F191" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G191" s="46" t="n">
+      <c r="F192" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H191" s="46" t="n">
+      <c r="H192" s="46" t="n">
         <v>-6.4</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="45" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-      <c r="B192" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C192" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D192" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F192" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G192" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H192" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="193">
@@ -13499,55 +13499,55 @@
       </c>
       <c r="C193" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D193" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F193" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H193" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="45" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B194" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C194" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D193" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E193" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F193" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G193" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H193" s="45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="46" t="inlineStr">
-        <is>
-          <t>Naime Cristina Freitas</t>
-        </is>
-      </c>
-      <c r="B194" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C194" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D194" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E194" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F194" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H194" s="46" t="n">
-        <v>-1.5</v>
+      <c r="D194" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E194" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -13563,23 +13563,23 @@
       </c>
       <c r="C195" s="46" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D195" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E195" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F195" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G195" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H195" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="196">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="C196" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D196" s="46" t="n">
@@ -13627,119 +13627,119 @@
       </c>
       <c r="C197" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D197" s="46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E197" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F197" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G197" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H197" s="46" t="n">
-        <v>-9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="45" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B198" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C198" s="45" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D198" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="E198" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H198" s="45" t="n">
-        <v>4</v>
+      <c r="A198" s="46" t="inlineStr">
+        <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B198" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C198" s="46" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D198" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F198" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H198" s="46" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="46" t="inlineStr">
         <is>
+          <t>Naime Cristina Freitas</t>
+        </is>
+      </c>
+      <c r="B199" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C199" s="46" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D199" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E199" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F199" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H199" s="46" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="45" t="inlineStr">
+        <is>
           <t>Rafael Ramos Recalde</t>
         </is>
       </c>
-      <c r="B199" s="46" t="inlineStr">
+      <c r="B200" s="45" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C199" s="46" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D199" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F199" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G199" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H199" s="46" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="46" t="inlineStr">
-        <is>
-          <t>Rafael Ramos Recalde</t>
-        </is>
-      </c>
-      <c r="B200" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C200" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D200" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F200" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G200" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H200" s="46" t="n">
-        <v>-0.6</v>
+      <c r="C200" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D200" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E200" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" s="45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="201">
@@ -13755,11 +13755,11 @@
       </c>
       <c r="C201" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D201" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E201" s="46" t="n">
         <v>0.3</v>
@@ -13771,7 +13771,7 @@
         <v>0.6</v>
       </c>
       <c r="H201" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="202">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="C202" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D202" s="46" t="n">
@@ -13819,23 +13819,23 @@
       </c>
       <c r="C203" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D203" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F203" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G203" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H203" s="46" t="n">
-        <v>-3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="204">
@@ -13851,151 +13851,151 @@
       </c>
       <c r="C204" s="46" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D204" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F204" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H204" s="46" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="46" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B205" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C205" s="46" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D205" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F205" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H205" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="46" t="inlineStr">
+        <is>
+          <t>Rafael Ramos Recalde</t>
+        </is>
+      </c>
+      <c r="B206" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C206" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D204" s="46" t="n">
+      <c r="D206" s="46" t="n">
         <v>106</v>
       </c>
-      <c r="E204" s="46" t="n">
+      <c r="E206" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F204" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G204" s="46" t="n">
+      <c r="F206" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G206" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H204" s="46" t="n">
+      <c r="H206" s="46" t="n">
         <v>-42.4</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="45" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="45" t="inlineStr">
         <is>
           <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
-      <c r="B205" s="45" t="inlineStr">
+      <c r="B207" s="45" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C205" s="45" t="inlineStr">
+      <c r="C207" s="45" t="inlineStr">
         <is>
           <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
-      <c r="D205" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E205" s="45" t="n">
+      <c r="D207" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="F205" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" s="45" t="n">
+      <c r="F207" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="H205" s="45" t="n">
+      <c r="H207" s="45" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="45" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="45" t="inlineStr">
         <is>
           <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
-      <c r="B206" s="45" t="inlineStr">
+      <c r="B208" s="45" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C206" s="45" t="inlineStr">
+      <c r="C208" s="45" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D206" s="45" t="n">
+      <c r="D208" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E206" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F206" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H206" s="45" t="n">
+      <c r="E208" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" s="45" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="46" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B207" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C207" s="46" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D207" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E207" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F207" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G207" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H207" s="46" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="46" t="inlineStr">
-        <is>
-          <t>Ramona dos Santos Oliveira</t>
-        </is>
-      </c>
-      <c r="B208" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C208" s="46" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D208" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E208" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F208" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G208" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H208" s="46" t="n">
-        <v>-1.2</v>
       </c>
     </row>
     <row r="209">
@@ -14011,11 +14011,11 @@
       </c>
       <c r="C209" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D209" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E209" s="46" t="n">
         <v>0.3</v>
@@ -14027,7 +14027,7 @@
         <v>0.6</v>
       </c>
       <c r="H209" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="210">
@@ -14043,119 +14043,119 @@
       </c>
       <c r="C210" s="46" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D210" s="46" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E210" s="46" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F210" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G210" s="46" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H210" s="46" t="n">
-        <v>-6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="45" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B211" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C211" s="45" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D211" s="45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E211" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F211" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G211" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H211" s="45" t="n">
-        <v>3</v>
+      <c r="A211" s="46" t="inlineStr">
+        <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B211" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C211" s="46" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D211" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E211" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F211" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H211" s="46" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="46" t="inlineStr">
         <is>
+          <t>Ramona dos Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="B212" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C212" s="46" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D212" s="46" t="n">
+        <v>15</v>
+      </c>
+      <c r="E212" s="46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F212" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G212" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H212" s="46" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="45" t="inlineStr">
+        <is>
           <t>Raquel Ortiz dos Santos</t>
         </is>
       </c>
-      <c r="B212" s="46" t="inlineStr">
+      <c r="B213" s="45" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C212" s="46" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D212" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E212" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F212" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G212" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H212" s="46" t="n">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="46" t="inlineStr">
-        <is>
-          <t>Raquel Ortiz dos Santos</t>
-        </is>
-      </c>
-      <c r="B213" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C213" s="46" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D213" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E213" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F213" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G213" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H213" s="46" t="n">
-        <v>-1.2</v>
+      <c r="C213" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D213" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E213" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F213" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" s="45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="214">
@@ -14171,23 +14171,23 @@
       </c>
       <c r="C214" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D214" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E214" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F214" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G214" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H214" s="46" t="n">
-        <v>-3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="215">
@@ -14203,151 +14203,151 @@
       </c>
       <c r="C215" s="46" t="inlineStr">
         <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D215" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E215" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F215" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H215" s="46" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="46" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B216" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C216" s="46" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D216" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F216" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H216" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="46" t="inlineStr">
+        <is>
+          <t>Raquel Ortiz dos Santos</t>
+        </is>
+      </c>
+      <c r="B217" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C217" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D215" s="46" t="n">
+      <c r="D217" s="46" t="n">
         <v>44</v>
       </c>
-      <c r="E215" s="46" t="n">
+      <c r="E217" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F215" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G215" s="46" t="n">
+      <c r="F217" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H215" s="46" t="n">
+      <c r="H217" s="46" t="n">
         <v>-17.6</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="45" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="45" t="inlineStr">
         <is>
           <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
-      <c r="B216" s="45" t="inlineStr">
+      <c r="B218" s="45" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C216" s="45" t="inlineStr">
+      <c r="C218" s="45" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D216" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E216" s="45" t="n">
+      <c r="D218" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="F216" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G216" s="45" t="n">
+      <c r="F218" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="H216" s="45" t="n">
+      <c r="H218" s="45" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="45" t="inlineStr">
+    <row r="219">
+      <c r="A219" s="45" t="inlineStr">
         <is>
           <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
-      <c r="B217" s="45" t="inlineStr">
+      <c r="B219" s="45" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C217" s="45" t="inlineStr">
+      <c r="C219" s="45" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D217" s="45" t="n">
+      <c r="D219" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E217" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F217" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G217" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H217" s="45" t="n">
+      <c r="E219" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H219" s="45" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="46" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B218" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C218" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D218" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E218" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F218" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G218" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H218" s="46" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="46" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="B219" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C219" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D219" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E219" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F219" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G219" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H219" s="46" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="220">
@@ -14363,23 +14363,23 @@
       </c>
       <c r="C220" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D220" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E220" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F220" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G220" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H220" s="46" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="221">
@@ -14395,119 +14395,119 @@
       </c>
       <c r="C221" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D221" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E221" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F221" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G221" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H221" s="46" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="45" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B222" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C222" s="45" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D222" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E222" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F222" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G222" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H222" s="45" t="n">
-        <v>2</v>
+      <c r="A222" s="46" t="inlineStr">
+        <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B222" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C222" s="46" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D222" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F222" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G222" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H222" s="46" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="46" t="inlineStr">
         <is>
+          <t>Rosalina Beniel Vargas</t>
+        </is>
+      </c>
+      <c r="B223" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C223" s="46" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D223" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F223" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H223" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="45" t="inlineStr">
+        <is>
           <t>Rozana Reis da Silva</t>
         </is>
       </c>
-      <c r="B223" s="46" t="inlineStr">
+      <c r="B224" s="45" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C223" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D223" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E223" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F223" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G223" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H223" s="46" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="46" t="inlineStr">
-        <is>
-          <t>Rozana Reis da Silva</t>
-        </is>
-      </c>
-      <c r="B224" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C224" s="46" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D224" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E224" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F224" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G224" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H224" s="46" t="n">
-        <v>-1.2</v>
+      <c r="C224" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D224" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E224" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -14523,23 +14523,23 @@
       </c>
       <c r="C225" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D225" s="46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E225" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F225" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G225" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H225" s="46" t="n">
-        <v>-2.4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="226">
@@ -14555,11 +14555,11 @@
       </c>
       <c r="C226" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D226" s="46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E226" s="46" t="n">
         <v>0.3</v>
@@ -14571,7 +14571,7 @@
         <v>0.6</v>
       </c>
       <c r="H226" s="46" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="227">
@@ -14587,23 +14587,23 @@
       </c>
       <c r="C227" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D227" s="46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E227" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F227" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G227" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H227" s="46" t="n">
-        <v>-3</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="228">
@@ -14619,151 +14619,151 @@
       </c>
       <c r="C228" s="46" t="inlineStr">
         <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D228" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E228" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F228" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G228" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H228" s="46" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="46" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="B229" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C229" s="46" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D229" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F229" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G229" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H229" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="46" t="inlineStr">
+        <is>
+          <t>Rozana Reis da Silva</t>
+        </is>
+      </c>
+      <c r="B230" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C230" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D228" s="46" t="n">
+      <c r="D230" s="46" t="n">
         <v>18</v>
       </c>
-      <c r="E228" s="46" t="n">
+      <c r="E230" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F228" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G228" s="46" t="n">
+      <c r="F230" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G230" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H228" s="46" t="n">
+      <c r="H230" s="46" t="n">
         <v>-7.2</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="45" t="inlineStr">
+    <row r="231">
+      <c r="A231" s="45" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B229" s="45" t="inlineStr">
+      <c r="B231" s="45" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C229" s="45" t="inlineStr">
+      <c r="C231" s="45" t="inlineStr">
         <is>
           <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
-      <c r="D229" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E229" s="45" t="n">
+      <c r="D231" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="F229" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G229" s="45" t="n">
+      <c r="F231" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="H229" s="45" t="n">
+      <c r="H231" s="45" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="45" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="45" t="inlineStr">
         <is>
           <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
-      <c r="B230" s="45" t="inlineStr">
+      <c r="B232" s="45" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C230" s="45" t="inlineStr">
+      <c r="C232" s="45" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D230" s="45" t="n">
+      <c r="D232" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E230" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F230" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G230" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H230" s="45" t="n">
+      <c r="E232" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H232" s="45" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="46" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B231" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C231" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D231" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E231" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F231" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G231" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H231" s="46" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="46" t="inlineStr">
-        <is>
-          <t>Rozentina Matos de Oliveira</t>
-        </is>
-      </c>
-      <c r="B232" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C232" s="46" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D232" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E232" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F232" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G232" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H232" s="46" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="233">
@@ -14779,23 +14779,23 @@
       </c>
       <c r="C233" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D233" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E233" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F233" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G233" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H233" s="46" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="234">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="C234" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D234" s="46" t="n">
@@ -14843,11 +14843,11 @@
       </c>
       <c r="C235" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D235" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E235" s="46" t="n">
         <v>0.3</v>
@@ -14859,7 +14859,7 @@
         <v>0.6</v>
       </c>
       <c r="H235" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="236">
@@ -14875,119 +14875,119 @@
       </c>
       <c r="C236" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D236" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E236" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F236" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G236" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H236" s="46" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="45" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B237" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C237" s="45" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D237" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E237" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F237" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G237" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H237" s="45" t="n">
-        <v>1</v>
+      <c r="A237" s="46" t="inlineStr">
+        <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B237" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C237" s="46" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D237" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E237" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F237" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G237" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H237" s="46" t="n">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="46" t="inlineStr">
         <is>
+          <t>Rozentina Matos de Oliveira</t>
+        </is>
+      </c>
+      <c r="B238" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C238" s="46" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D238" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E238" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F238" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G238" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H238" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="45" t="inlineStr">
+        <is>
           <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
-      <c r="B238" s="46" t="inlineStr">
+      <c r="B239" s="45" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C238" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D238" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E238" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F238" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G238" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H238" s="46" t="n">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="46" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="B239" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C239" s="46" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D239" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E239" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F239" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G239" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H239" s="46" t="n">
-        <v>-0.6</v>
+      <c r="C239" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D239" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E239" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G239" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H239" s="45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -15003,23 +15003,23 @@
       </c>
       <c r="C240" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D240" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E240" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F240" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G240" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H240" s="46" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="241">
@@ -15035,23 +15035,23 @@
       </c>
       <c r="C241" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D241" s="46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E241" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F241" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G241" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H241" s="46" t="n">
-        <v>-15</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="242">
@@ -15067,23 +15067,23 @@
       </c>
       <c r="C242" s="46" t="inlineStr">
         <is>
-          <t>Visita em sequência suspeita</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D242" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" s="46" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="F242" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G242" s="46" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="H242" s="46" t="n">
-        <v>-4</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="243">
@@ -15099,23 +15099,23 @@
       </c>
       <c r="C243" s="46" t="inlineStr">
         <is>
-          <t>Visita fora do expediente/fim de semana</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D243" s="46" t="n">
         <v>5</v>
       </c>
       <c r="E243" s="46" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F243" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G243" s="46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H243" s="46" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="244">
@@ -15131,87 +15131,87 @@
       </c>
       <c r="C244" s="46" t="inlineStr">
         <is>
+          <t>Visita em sequência suspeita</t>
+        </is>
+      </c>
+      <c r="D244" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E244" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G244" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H244" s="46" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="46" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B245" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C245" s="46" t="inlineStr">
+        <is>
+          <t>Visita fora do expediente/fim de semana</t>
+        </is>
+      </c>
+      <c r="D245" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E245" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F245" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G245" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H245" s="46" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="46" t="inlineStr">
+        <is>
+          <t>Sara Eliane Talaveira de Oliveira</t>
+        </is>
+      </c>
+      <c r="B246" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C246" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D244" s="46" t="n">
+      <c r="D246" s="46" t="n">
         <v>8</v>
       </c>
-      <c r="E244" s="46" t="n">
+      <c r="E246" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F244" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G244" s="46" t="n">
+      <c r="F246" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G246" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H244" s="46" t="n">
+      <c r="H246" s="46" t="n">
         <v>-3.2</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="45" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B245" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C245" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D245" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E245" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F245" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G245" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H245" s="45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="45" t="inlineStr">
-        <is>
-          <t>Selba Ramona Afonso</t>
-        </is>
-      </c>
-      <c r="B246" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 3</t>
-        </is>
-      </c>
-      <c r="C246" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D246" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E246" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F246" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G246" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H246" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="247">
@@ -15227,66 +15227,66 @@
       </c>
       <c r="C247" s="45" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
         </is>
       </c>
       <c r="D247" s="45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E247" s="45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F247" s="45" t="n">
         <v>1</v>
       </c>
       <c r="G247" s="45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H247" s="45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="46" t="inlineStr">
+      <c r="A248" s="45" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="B248" s="46" t="inlineStr">
+      <c r="B248" s="45" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="C248" s="46" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D248" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E248" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F248" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G248" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H248" s="46" t="n">
-        <v>-0.6</v>
+      <c r="C248" s="45" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D248" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E248" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F248" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H248" s="45" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="45" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="B249" s="45" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C249" s="45" t="inlineStr">
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="D249" s="45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E249" s="45" t="n">
         <v>1</v>
@@ -15307,71 +15307,71 @@
         <v>1</v>
       </c>
       <c r="H249" s="45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="46" t="inlineStr">
         <is>
+          <t>Selba Ramona Afonso</t>
+        </is>
+      </c>
+      <c r="B250" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="C250" s="46" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D250" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F250" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G250" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H250" s="46" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="45" t="inlineStr">
+        <is>
           <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
-      <c r="B250" s="46" t="inlineStr">
+      <c r="B251" s="45" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C250" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D250" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E250" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F250" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G250" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H250" s="46" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="46" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="B251" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C251" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D251" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E251" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F251" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G251" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H251" s="46" t="n">
-        <v>-0.6</v>
+      <c r="C251" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D251" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E251" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G251" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H251" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -15387,23 +15387,23 @@
       </c>
       <c r="C252" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D252" s="46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E252" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F252" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G252" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H252" s="46" t="n">
-        <v>-1.8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="253">
@@ -15419,11 +15419,11 @@
       </c>
       <c r="C253" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D253" s="46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E253" s="46" t="n">
         <v>0.3</v>
@@ -15435,7 +15435,7 @@
         <v>0.6</v>
       </c>
       <c r="H253" s="46" t="n">
-        <v>-2.4</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="254">
@@ -15451,23 +15451,23 @@
       </c>
       <c r="C254" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D254" s="46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E254" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F254" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G254" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H254" s="46" t="n">
-        <v>-3</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="255">
@@ -15483,87 +15483,87 @@
       </c>
       <c r="C255" s="46" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D255" s="46" t="n">
         <v>4</v>
       </c>
       <c r="E255" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F255" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G255" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H255" s="46" t="n">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="46" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B256" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C256" s="46" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D256" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E256" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F256" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G256" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H256" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="46" t="inlineStr">
+        <is>
+          <t>Silvina Regina de Souza Valiente</t>
+        </is>
+      </c>
+      <c r="B257" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C257" s="46" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D257" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E257" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F255" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G255" s="46" t="n">
+      <c r="F257" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G257" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H255" s="46" t="n">
+      <c r="H257" s="46" t="n">
         <v>-1.6</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="45" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B256" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C256" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhum turno sem lançamento no período</t>
-        </is>
-      </c>
-      <c r="D256" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E256" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F256" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G256" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H256" s="45" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="45" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B257" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C257" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D257" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E257" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F257" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G257" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H257" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="258">
@@ -15579,125 +15579,125 @@
       </c>
       <c r="C258" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhum turno sem lançamento no período</t>
+        </is>
+      </c>
+      <c r="D258" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E258" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F258" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G258" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H258" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="45" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B259" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C259" s="45" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D259" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E259" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F259" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G259" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H259" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="45" t="inlineStr">
+        <is>
+          <t>Suely Aguiar Alves Luiz</t>
+        </is>
+      </c>
+      <c r="B260" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C260" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D258" s="45" t="n">
+      <c r="D260" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="E258" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F258" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G258" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H258" s="45" t="n">
+      <c r="E260" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G260" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H260" s="45" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="46" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="46" t="inlineStr">
         <is>
           <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
-      <c r="B259" s="46" t="inlineStr">
+      <c r="B261" s="46" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C259" s="46" t="inlineStr">
+      <c r="C261" s="46" t="inlineStr">
         <is>
           <t>Início manhã após 08h30</t>
         </is>
       </c>
-      <c r="D259" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E259" s="46" t="n">
+      <c r="D261" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E261" s="46" t="n">
         <v>0.3</v>
       </c>
-      <c r="F259" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G259" s="46" t="n">
+      <c r="F261" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G261" s="46" t="n">
         <v>0.6</v>
       </c>
-      <c r="H259" s="46" t="n">
+      <c r="H261" s="46" t="n">
         <v>-0.6</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="46" t="inlineStr">
-        <is>
-          <t>Suely Aguiar Alves Luiz</t>
-        </is>
-      </c>
-      <c r="B260" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C260" s="46" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D260" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E260" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F260" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G260" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H260" s="46" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="45" t="inlineStr">
-        <is>
-          <t>Teonilda Florentino Vieira</t>
-        </is>
-      </c>
-      <c r="B261" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C261" s="45" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D261" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E261" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F261" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G261" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H261" s="45" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="46" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Suely Aguiar Alves Luiz</t>
         </is>
       </c>
       <c r="B262" s="46" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="C262" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D262" s="46" t="n">
@@ -15727,35 +15727,35 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="46" t="inlineStr">
+      <c r="A263" s="45" t="inlineStr">
         <is>
           <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
-      <c r="B263" s="46" t="inlineStr">
+      <c r="B263" s="45" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C263" s="46" t="inlineStr">
-        <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
-        </is>
-      </c>
-      <c r="D263" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="E263" s="46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F263" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G263" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="H263" s="46" t="n">
-        <v>-12</v>
+      <c r="C263" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D263" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E263" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F263" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G263" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" s="45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -15771,119 +15771,119 @@
       </c>
       <c r="C264" s="46" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D264" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F264" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G264" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H264" s="46" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="46" t="inlineStr">
+        <is>
+          <t>Teonilda Florentino Vieira</t>
+        </is>
+      </c>
+      <c r="B265" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C265" s="46" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D265" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E265" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F265" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G265" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E264" s="46" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F264" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G264" s="46" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H264" s="46" t="n">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="45" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B265" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C265" s="45" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D265" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E265" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F265" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G265" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H265" s="45" t="n">
-        <v>2</v>
+      <c r="H265" s="46" t="n">
+        <v>-12</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="46" t="inlineStr">
         <is>
+          <t>Teonilda Florentino Vieira</t>
+        </is>
+      </c>
+      <c r="B266" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C266" s="46" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D266" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E266" s="46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F266" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G266" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H266" s="46" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="45" t="inlineStr">
+        <is>
           <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
-      <c r="B266" s="46" t="inlineStr">
+      <c r="B267" s="45" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C266" s="46" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D266" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E266" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F266" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G266" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H266" s="46" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="46" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B267" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C267" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D267" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E267" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F267" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G267" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H267" s="46" t="n">
-        <v>-0.6</v>
+      <c r="C267" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D267" s="45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F267" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G267" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H267" s="45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="268">
@@ -15899,23 +15899,23 @@
       </c>
       <c r="C268" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D268" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E268" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F268" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G268" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H268" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="269">
@@ -15931,23 +15931,23 @@
       </c>
       <c r="C269" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D269" s="46" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E269" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F269" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G269" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H269" s="46" t="n">
-        <v>-12</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="270">
@@ -15963,151 +15963,151 @@
       </c>
       <c r="C270" s="46" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D270" s="46" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E270" s="46" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F270" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G270" s="46" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H270" s="46" t="n">
-        <v>-4.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="45" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B271" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C271" s="45" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D271" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E271" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F271" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G271" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H271" s="45" t="n">
-        <v>1</v>
+      <c r="A271" s="46" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B271" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C271" s="46" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D271" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E271" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F271" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G271" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H271" s="46" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="46" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B272" s="46" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C272" s="46" t="inlineStr">
         <is>
-          <t>Dia sem bater a meta diária</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D272" s="46" t="n">
         <v>2</v>
       </c>
       <c r="E272" s="46" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F272" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G272" s="46" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H272" s="46" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="46" t="inlineStr">
         <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B273" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C273" s="46" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D273" s="46" t="n">
+        <v>13</v>
+      </c>
+      <c r="E273" s="46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F273" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G273" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H273" s="46" t="n">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="45" t="inlineStr">
+        <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B273" s="46" t="inlineStr">
+      <c r="B274" s="45" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C273" s="46" t="inlineStr">
-        <is>
-          <t>Fim manhã antes de 10h00</t>
-        </is>
-      </c>
-      <c r="D273" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E273" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F273" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G273" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H273" s="46" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="46" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B274" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C274" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D274" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E274" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F274" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G274" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H274" s="46" t="n">
-        <v>-0.6</v>
+      <c r="C274" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D274" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F274" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G274" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H274" s="45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -16123,23 +16123,23 @@
       </c>
       <c r="C275" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D275" s="46" t="n">
         <v>2</v>
       </c>
       <c r="E275" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F275" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G275" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H275" s="46" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="276">
@@ -16155,23 +16155,23 @@
       </c>
       <c r="C276" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D276" s="46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E276" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F276" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G276" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H276" s="46" t="n">
-        <v>-9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="277">
@@ -16187,151 +16187,151 @@
       </c>
       <c r="C277" s="46" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D277" s="46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E277" s="46" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F277" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G277" s="46" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H277" s="46" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="46" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B278" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C278" s="46" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D278" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E278" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F278" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G278" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H278" s="46" t="n">
         <v>-1.2</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="45" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B278" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C278" s="45" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D278" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="E278" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F278" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G278" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H278" s="45" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="46" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="B279" s="46" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C279" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D279" s="46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E279" s="46" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="F279" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G279" s="46" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="H279" s="46" t="n">
-        <v>-0.6</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="46" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="B280" s="46" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C280" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Visita rápida</t>
         </is>
       </c>
       <c r="D280" s="46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E280" s="46" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F280" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G280" s="46" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H280" s="46" t="n">
         <v>-1.2</v>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="46" t="inlineStr">
+      <c r="A281" s="45" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B281" s="46" t="inlineStr">
+      <c r="B281" s="45" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C281" s="46" t="inlineStr">
-        <is>
-          <t>Início tarde após 14h30</t>
-        </is>
-      </c>
-      <c r="D281" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E281" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F281" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G281" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H281" s="46" t="n">
-        <v>-0.6</v>
+      <c r="C281" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D281" s="45" t="n">
+        <v>4</v>
+      </c>
+      <c r="E281" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F281" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G281" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H281" s="45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="282">
@@ -16347,23 +16347,23 @@
       </c>
       <c r="C282" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D282" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E282" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F282" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G282" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H282" s="46" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="283">
@@ -16379,183 +16379,183 @@
       </c>
       <c r="C283" s="46" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D283" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E283" s="46" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F283" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G283" s="46" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H283" s="46" t="n">
-        <v>-0.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="45" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B284" s="45" t="inlineStr">
+      <c r="A284" s="46" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B284" s="46" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C284" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D284" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E284" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F284" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G284" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H284" s="45" t="n">
-        <v>5</v>
+      <c r="C284" s="46" t="inlineStr">
+        <is>
+          <t>Início tarde após 14h30</t>
+        </is>
+      </c>
+      <c r="D284" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E284" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F284" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G284" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H284" s="46" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="45" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B285" s="45" t="inlineStr">
+      <c r="A285" s="46" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B285" s="46" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C285" s="45" t="inlineStr">
-        <is>
-          <t>Dia com meta diária batida</t>
-        </is>
-      </c>
-      <c r="D285" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E285" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F285" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G285" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H285" s="45" t="n">
-        <v>2</v>
+      <c r="C285" s="46" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D285" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E285" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F285" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G285" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H285" s="46" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="46" t="inlineStr">
         <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B286" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C286" s="46" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D286" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" s="46" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F286" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G286" s="46" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H286" s="46" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="45" t="inlineStr">
+        <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B286" s="46" t="inlineStr">
+      <c r="B287" s="45" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C286" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D286" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E286" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F286" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G286" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H286" s="46" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="46" t="inlineStr">
+      <c r="C287" s="45" t="inlineStr">
+        <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D287" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E287" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F287" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G287" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H287" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="45" t="inlineStr">
         <is>
           <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
-      <c r="B287" s="46" t="inlineStr">
+      <c r="B288" s="45" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C287" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D287" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E287" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F287" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G287" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H287" s="46" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="46" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B288" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C288" s="46" t="inlineStr">
-        <is>
-          <t>Início manhã após 08h30</t>
-        </is>
-      </c>
-      <c r="D288" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="E288" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F288" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G288" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H288" s="46" t="n">
-        <v>-1.8</v>
+      <c r="C288" s="45" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D288" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E288" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F288" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G288" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H288" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -16571,22 +16571,118 @@
       </c>
       <c r="C289" s="46" t="inlineStr">
         <is>
+          <t>Dia sem bater a meta diária</t>
+        </is>
+      </c>
+      <c r="D289" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E289" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F289" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G289" s="46" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H289" s="46" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="46" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B290" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C290" s="46" t="inlineStr">
+        <is>
+          <t>Fim tarde antes de 16h00</t>
+        </is>
+      </c>
+      <c r="D290" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E290" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F290" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G290" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H290" s="46" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="46" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B291" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C291" s="46" t="inlineStr">
+        <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D291" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E291" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F291" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G291" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H291" s="46" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="46" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B292" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C292" s="46" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D289" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E289" s="46" t="n">
+      <c r="D292" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E292" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="F289" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G289" s="46" t="n">
+      <c r="F292" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G292" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="H289" s="46" t="n">
+      <c r="H292" s="46" t="n">
         <v>-3</v>
       </c>
     </row>
@@ -17004,36 +17100,36 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5.63</v>
+        <v>5.52</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>Q002, Q007, Q008, Q009, Q010, Q015, Q018, Q019, Q020, Q021, Q033</t>
+          <t>Q002, Q007, Q008, Q009, Q010, Q012, Q015, Q018, Q019, Q020, Q021, Q025, Q030, Q033</t>
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>11.27</v>
+        <v>11.11</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>36.04</v>
+        <v>31.3</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -17220,36 +17316,36 @@
         </is>
       </c>
       <c r="D12" s="5" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4.05</v>
+        <v>4.36</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>4</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>Q003, Q004</t>
+          <t>Q003, Q004, Q011</t>
         </is>
       </c>
       <c r="I12" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>16.67</v>
+        <v>13.13</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>12</v>
+        <v>15.38</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
@@ -17490,20 +17586,20 @@
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.220000000000001</v>
+        <v>9.16</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>9</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Q002, Q004</t>
+          <t>Q002, Q003, Q004</t>
         </is>
       </c>
       <c r="I17" s="4" t="n">
@@ -17519,7 +17615,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>11.21</v>
+        <v>8.33</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
@@ -18246,20 +18342,20 @@
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.81</v>
+        <v>5.69</v>
       </c>
       <c r="F31" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G31" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="G31" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>Q006, Q007, Q008, Q009, Q010</t>
+          <t>Q006, Q007, Q008, Q009, Q010, Q011</t>
         </is>
       </c>
       <c r="I31" s="4" t="n">
@@ -18269,13 +18365,13 @@
         <v>0</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L31" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>45.61</v>
+        <v>42.47</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
@@ -23010,7 +23106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23025,7 +23121,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (68 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (61 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -23319,11 +23415,11 @@
     </row>
     <row r="10">
       <c r="A10" s="34" t="n">
-        <v>116</v>
+        <v>85</v>
       </c>
       <c r="B10" s="34" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C10" s="34" t="inlineStr">
@@ -23333,17 +23429,17 @@
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E10" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F10" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G10" s="34" t="inlineStr">
@@ -23378,7 +23474,7 @@
       </c>
       <c r="F11" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G11" s="34" t="inlineStr">
@@ -23389,11 +23485,11 @@
     </row>
     <row r="12">
       <c r="A12" s="34" t="n">
-        <v>3037</v>
+        <v>30</v>
       </c>
       <c r="B12" s="34" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Rozentina Matos de Oliveira</t>
         </is>
       </c>
       <c r="C12" s="34" t="inlineStr">
@@ -23413,7 +23509,7 @@
       </c>
       <c r="F12" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G12" s="34" t="inlineStr">
@@ -23448,7 +23544,7 @@
       </c>
       <c r="F13" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G13" s="34" t="inlineStr">
@@ -23459,31 +23555,31 @@
     </row>
     <row r="14">
       <c r="A14" s="34" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Brauher Luiz Alvarenga Gonzalez</t>
         </is>
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D14" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E14" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F14" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G14" s="34" t="inlineStr">
@@ -23494,31 +23590,31 @@
     </row>
     <row r="15">
       <c r="A15" s="34" t="n">
-        <v>3037</v>
+        <v>2030</v>
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E15" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F15" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G15" s="34" t="inlineStr">
@@ -23529,31 +23625,31 @@
     </row>
     <row r="16">
       <c r="A16" s="34" t="n">
-        <v>30</v>
+        <v>2917</v>
       </c>
       <c r="B16" s="34" t="inlineStr">
         <is>
-          <t>Rozentina Matos de Oliveira</t>
+          <t>Bianca Afonso Narbaez</t>
         </is>
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E16" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F16" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G16" s="34" t="inlineStr">
@@ -23564,31 +23660,31 @@
     </row>
     <row r="17">
       <c r="A17" s="34" t="n">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Fabiana de Figueredo Vieira</t>
         </is>
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D17" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E17" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F17" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G17" s="34" t="inlineStr">
@@ -23599,11 +23695,11 @@
     </row>
     <row r="18">
       <c r="A18" s="34" t="n">
-        <v>125</v>
+        <v>3127</v>
       </c>
       <c r="B18" s="34" t="inlineStr">
         <is>
-          <t>Brauher Luiz Alvarenga Gonzalez</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C18" s="34" t="inlineStr">
@@ -23613,12 +23709,12 @@
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E18" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
@@ -23648,12 +23744,12 @@
       </c>
       <c r="D19" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F19" s="34" t="inlineStr">
@@ -23669,11 +23765,11 @@
     </row>
     <row r="20">
       <c r="A20" s="34" t="n">
-        <v>2917</v>
+        <v>3035</v>
       </c>
       <c r="B20" s="34" t="inlineStr">
         <is>
-          <t>Bianca Afonso Narbaez</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C20" s="34" t="inlineStr">
@@ -23704,11 +23800,11 @@
     </row>
     <row r="21">
       <c r="A21" s="34" t="n">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>Fabiana de Figueredo Vieira</t>
+          <t>Wesley de Souza Leal</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
@@ -23739,11 +23835,11 @@
     </row>
     <row r="22">
       <c r="A22" s="34" t="n">
-        <v>3127</v>
+        <v>142</v>
       </c>
       <c r="B22" s="34" t="inlineStr">
         <is>
-          <t>Gisele Olimpia Torres</t>
+          <t>William Anderson Chamorro Tavares</t>
         </is>
       </c>
       <c r="C22" s="34" t="inlineStr">
@@ -23774,11 +23870,11 @@
     </row>
     <row r="23">
       <c r="A23" s="34" t="n">
-        <v>2030</v>
+        <v>3035</v>
       </c>
       <c r="B23" s="34" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
@@ -23798,7 +23894,7 @@
       </c>
       <c r="F23" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G23" s="34" t="inlineStr">
@@ -23823,12 +23919,12 @@
       </c>
       <c r="D24" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F24" s="34" t="inlineStr">
@@ -23844,11 +23940,11 @@
     </row>
     <row r="25">
       <c r="A25" s="34" t="n">
-        <v>81</v>
+        <v>2030</v>
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>Wesley de Souza Leal</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
@@ -23858,17 +23954,17 @@
       </c>
       <c r="D25" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G25" s="34" t="inlineStr">
@@ -23879,11 +23975,11 @@
     </row>
     <row r="26">
       <c r="A26" s="34" t="n">
-        <v>142</v>
+        <v>3035</v>
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>William Anderson Chamorro Tavares</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C26" s="34" t="inlineStr">
@@ -23893,17 +23989,17 @@
       </c>
       <c r="D26" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G26" s="34" t="inlineStr">
@@ -23914,31 +24010,31 @@
     </row>
     <row r="27">
       <c r="A27" s="34" t="n">
-        <v>3035</v>
+        <v>1938</v>
       </c>
       <c r="B27" s="34" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C27" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D27" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G27" s="34" t="inlineStr">
@@ -23949,26 +24045,26 @@
     </row>
     <row r="28">
       <c r="A28" s="34" t="n">
-        <v>151</v>
+        <v>1938</v>
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D28" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F28" s="34" t="inlineStr">
@@ -23984,31 +24080,31 @@
     </row>
     <row r="29">
       <c r="A29" s="34" t="n">
-        <v>3035</v>
+        <v>1938</v>
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G29" s="34" t="inlineStr">
@@ -24019,26 +24115,26 @@
     </row>
     <row r="30">
       <c r="A30" s="34" t="n">
-        <v>151</v>
+        <v>3038</v>
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>Gilmar Bitencourt Luiz</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E30" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F30" s="34" t="inlineStr">
@@ -24054,31 +24150,31 @@
     </row>
     <row r="31">
       <c r="A31" s="34" t="n">
-        <v>2030</v>
+        <v>2918</v>
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D31" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E31" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F31" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G31" s="34" t="inlineStr">
@@ -24089,31 +24185,31 @@
     </row>
     <row r="32">
       <c r="A32" s="34" t="n">
-        <v>3035</v>
+        <v>120</v>
       </c>
       <c r="B32" s="34" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D32" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E32" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G32" s="34" t="inlineStr">
@@ -24124,11 +24220,11 @@
     </row>
     <row r="33">
       <c r="A33" s="34" t="n">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C33" s="34" t="inlineStr">
@@ -24138,12 +24234,12 @@
       </c>
       <c r="D33" s="34" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E33" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F33" s="34" t="inlineStr">
@@ -24173,12 +24269,12 @@
       </c>
       <c r="D34" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E34" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F34" s="34" t="inlineStr">
@@ -24194,11 +24290,11 @@
     </row>
     <row r="35">
       <c r="A35" s="34" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C35" s="34" t="inlineStr">
@@ -24208,17 +24304,17 @@
       </c>
       <c r="D35" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E35" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G35" s="34" t="inlineStr">
@@ -24229,11 +24325,11 @@
     </row>
     <row r="36">
       <c r="A36" s="34" t="n">
-        <v>3038</v>
+        <v>3128</v>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C36" s="34" t="inlineStr">
@@ -24243,17 +24339,17 @@
       </c>
       <c r="D36" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E36" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G36" s="34" t="inlineStr">
@@ -24288,7 +24384,7 @@
       </c>
       <c r="F37" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G37" s="34" t="inlineStr">
@@ -24323,7 +24419,7 @@
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G38" s="34" t="inlineStr">
@@ -24334,11 +24430,11 @@
     </row>
     <row r="39">
       <c r="A39" s="34" t="n">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="B39" s="34" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C39" s="34" t="inlineStr">
@@ -24358,7 +24454,7 @@
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G39" s="34" t="inlineStr">
@@ -24369,11 +24465,11 @@
     </row>
     <row r="40">
       <c r="A40" s="34" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B40" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C40" s="34" t="inlineStr">
@@ -24383,12 +24479,12 @@
       </c>
       <c r="D40" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E40" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F40" s="34" t="inlineStr">
@@ -24404,11 +24500,11 @@
     </row>
     <row r="41">
       <c r="A41" s="34" t="n">
-        <v>3038</v>
+        <v>1938</v>
       </c>
       <c r="B41" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C41" s="34" t="inlineStr">
@@ -24418,12 +24514,12 @@
       </c>
       <c r="D41" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E41" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F41" s="34" t="inlineStr">
@@ -24439,11 +24535,11 @@
     </row>
     <row r="42">
       <c r="A42" s="34" t="n">
-        <v>3128</v>
+        <v>2918</v>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C42" s="34" t="inlineStr">
@@ -24453,17 +24549,17 @@
       </c>
       <c r="D42" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E42" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G42" s="34" t="inlineStr">
@@ -24474,11 +24570,11 @@
     </row>
     <row r="43">
       <c r="A43" s="34" t="n">
-        <v>2918</v>
+        <v>1938</v>
       </c>
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C43" s="34" t="inlineStr">
@@ -24488,12 +24584,12 @@
       </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F43" s="34" t="inlineStr">
@@ -24509,31 +24605,31 @@
     </row>
     <row r="44">
       <c r="A44" s="34" t="n">
-        <v>120</v>
+        <v>2789</v>
       </c>
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E44" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G44" s="34" t="inlineStr">
@@ -24544,31 +24640,31 @@
     </row>
     <row r="45">
       <c r="A45" s="34" t="n">
-        <v>1938</v>
+        <v>149</v>
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E45" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G45" s="34" t="inlineStr">
@@ -24579,26 +24675,26 @@
     </row>
     <row r="46">
       <c r="A46" s="34" t="n">
-        <v>2918</v>
+        <v>1996</v>
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E46" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F46" s="34" t="inlineStr">
@@ -24614,31 +24710,31 @@
     </row>
     <row r="47">
       <c r="A47" s="34" t="n">
-        <v>1938</v>
+        <v>110</v>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E47" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F47" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G47" s="34" t="inlineStr">
@@ -24649,26 +24745,26 @@
     </row>
     <row r="48">
       <c r="A48" s="34" t="n">
-        <v>2918</v>
+        <v>2789</v>
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C48" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E48" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
@@ -24684,26 +24780,26 @@
     </row>
     <row r="49">
       <c r="A49" s="34" t="n">
-        <v>1938</v>
+        <v>1996</v>
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
@@ -24719,31 +24815,31 @@
     </row>
     <row r="50">
       <c r="A50" s="34" t="n">
-        <v>3038</v>
+        <v>110</v>
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E50" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G50" s="34" t="inlineStr">
@@ -24754,11 +24850,11 @@
     </row>
     <row r="51">
       <c r="A51" s="34" t="n">
-        <v>2789</v>
+        <v>80</v>
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C51" s="34" t="inlineStr">
@@ -24768,12 +24864,12 @@
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E51" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F51" s="34" t="inlineStr">
@@ -24789,11 +24885,11 @@
     </row>
     <row r="52">
       <c r="A52" s="34" t="n">
-        <v>149</v>
+        <v>2789</v>
       </c>
       <c r="B52" s="34" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C52" s="34" t="inlineStr">
@@ -24803,12 +24899,12 @@
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E52" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F52" s="34" t="inlineStr">
@@ -24824,11 +24920,11 @@
     </row>
     <row r="53">
       <c r="A53" s="34" t="n">
-        <v>1996</v>
+        <v>149</v>
       </c>
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
@@ -24838,12 +24934,12 @@
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E53" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F53" s="34" t="inlineStr">
@@ -24859,11 +24955,11 @@
     </row>
     <row r="54">
       <c r="A54" s="34" t="n">
-        <v>110</v>
+        <v>1942</v>
       </c>
       <c r="B54" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
@@ -24873,17 +24969,17 @@
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E54" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G54" s="34" t="inlineStr">
@@ -24894,11 +24990,11 @@
     </row>
     <row r="55">
       <c r="A55" s="34" t="n">
-        <v>2789</v>
+        <v>161</v>
       </c>
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
@@ -24908,17 +25004,17 @@
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E55" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F55" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G55" s="34" t="inlineStr">
@@ -24943,17 +25039,17 @@
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E56" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G56" s="34" t="inlineStr">
@@ -24964,11 +25060,11 @@
     </row>
     <row r="57">
       <c r="A57" s="34" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
@@ -24999,11 +25095,11 @@
     </row>
     <row r="58">
       <c r="A58" s="34" t="n">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="B58" s="34" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C58" s="34" t="inlineStr">
@@ -25058,7 +25154,7 @@
       </c>
       <c r="F59" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G59" s="34" t="inlineStr">
@@ -25069,11 +25165,11 @@
     </row>
     <row r="60">
       <c r="A60" s="34" t="n">
-        <v>149</v>
+        <v>1996</v>
       </c>
       <c r="B60" s="34" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C60" s="34" t="inlineStr">
@@ -25083,12 +25179,12 @@
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F60" s="34" t="inlineStr">
@@ -25104,11 +25200,11 @@
     </row>
     <row r="61">
       <c r="A61" s="34" t="n">
-        <v>1942</v>
+        <v>157</v>
       </c>
       <c r="B61" s="34" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C61" s="34" t="inlineStr">
@@ -25118,12 +25214,12 @@
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F61" s="34" t="inlineStr">
@@ -25139,11 +25235,11 @@
     </row>
     <row r="62">
       <c r="A62" s="34" t="n">
-        <v>161</v>
+        <v>1996</v>
       </c>
       <c r="B62" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C62" s="34" t="inlineStr">
@@ -25153,17 +25249,17 @@
       </c>
       <c r="D62" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E62" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F62" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G62" s="34" t="inlineStr">
@@ -25174,11 +25270,11 @@
     </row>
     <row r="63">
       <c r="A63" s="34" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B63" s="34" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C63" s="34" t="inlineStr">
@@ -25188,17 +25284,17 @@
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F63" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G63" s="34" t="inlineStr">
@@ -25207,253 +25303,8 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="34" t="n">
-        <v>86</v>
-      </c>
-      <c r="B64" s="34" t="inlineStr">
-        <is>
-          <t>Silvina Regina de Souza Valiente</t>
-        </is>
-      </c>
-      <c r="C64" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="E64" s="34" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F64" s="34" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G64" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="34" t="n">
-        <v>157</v>
-      </c>
-      <c r="B65" s="34" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C65" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D65" s="34" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="E65" s="34" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F65" s="34" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G65" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="34" t="n">
-        <v>2789</v>
-      </c>
-      <c r="B66" s="34" t="inlineStr">
-        <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
-        </is>
-      </c>
-      <c r="C66" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D66" s="34" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
-        </is>
-      </c>
-      <c r="E66" s="34" t="inlineStr">
-        <is>
-          <t>Quinta</t>
-        </is>
-      </c>
-      <c r="F66" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G66" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="34" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B67" s="34" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C67" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D67" s="34" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E67" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F67" s="34" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G67" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="34" t="n">
-        <v>157</v>
-      </c>
-      <c r="B68" s="34" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C68" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D68" s="34" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E68" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F68" s="34" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G68" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="34" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B69" s="34" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C69" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D69" s="34" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E69" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F69" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G69" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="34" t="n">
-        <v>157</v>
-      </c>
-      <c r="B70" s="34" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C70" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D70" s="34" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E70" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F70" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G70" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G70"/>
+  <autoFilter ref="A2:G63"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_323.xlsx
+++ b/data/historico/semana_323.xlsx
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 20min'!$A$2:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$41</definedName>
@@ -2885,16 +2885,16 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>39</v>
+        <v>29.5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>4.9</v>
+        <v>5.12</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>5</v>
@@ -2903,7 +2903,7 @@
         <v>3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>7.69</v>
+        <v>5.08</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -2927,49 +2927,49 @@
         <v>0</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="S21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>26.42</v>
+        <v>22.37</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>5.83</v>
+        <v>5.09</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>5.83</v>
+        <v>10.18</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>3.18</v>
+        <v>2.52</v>
       </c>
       <c r="Y21" s="4" t="inlineStr">
         <is>
-          <t>R$ 69,44</t>
+          <t>R$ 87,83</t>
         </is>
       </c>
       <c r="Z21" s="4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA21" s="4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AB21" s="4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC21" s="4" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:39</t>
         </is>
       </c>
     </row>
@@ -4767,25 +4767,25 @@
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>6.16</v>
+        <v>6.59</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>8</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>17.78</v>
+        <v>11.59</v>
       </c>
       <c r="K39" s="5" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>0</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N39" s="5" t="n">
         <v>0</v>
@@ -4809,39 +4809,39 @@
         <v>5</v>
       </c>
       <c r="R39" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="5" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="U39" s="5" t="n">
-        <v>13.46</v>
+        <v>10.39</v>
       </c>
       <c r="V39" s="5" t="n">
-        <v>9.35</v>
+        <v>7.3</v>
       </c>
       <c r="W39" s="5" t="n">
-        <v>18.7</v>
+        <v>21.9</v>
       </c>
       <c r="X39" s="5" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="Y39" s="5" t="inlineStr">
         <is>
-          <t>R$ 95,76</t>
+          <t>R$ 87,45</t>
         </is>
       </c>
       <c r="Z39" s="5" t="inlineStr">
         <is>
-          <t>05:19</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AA39" s="5" t="inlineStr">
         <is>
-          <t>06:47</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AB39" s="5" t="inlineStr">
@@ -5918,19 +5918,19 @@
         </is>
       </c>
       <c r="C21" s="25" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="D21" s="25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E21" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="25" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>26.42</v>
+        <v>22.37</v>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
@@ -6440,19 +6440,19 @@
         </is>
       </c>
       <c r="C39" s="25" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D39" s="25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="25" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="G39" s="25" t="n">
-        <v>13.46</v>
+        <v>10.39</v>
       </c>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="n"/>
@@ -6527,19 +6527,19 @@
         </is>
       </c>
       <c r="C42" s="37" t="n">
-        <v>3446</v>
+        <v>3490</v>
       </c>
       <c r="D42" s="37" t="n">
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="E42" s="37" t="n">
         <v>6</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>4755</v>
+        <v>4803</v>
       </c>
       <c r="G42" s="37" t="n">
-        <v>27.53</v>
+        <v>27.34</v>
       </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
@@ -7389,7 +7389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8072,25 +8072,25 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>8</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>92.8</v>
+        <v>93</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -8104,25 +8104,25 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>91.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -8136,12 +8136,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
@@ -8154,43 +8154,43 @@
         <v>1</v>
       </c>
       <c r="G24" s="4" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="4" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
         </is>
       </c>
     </row>
@@ -8200,25 +8200,25 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>88</v>
+        <v>89.8</v>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -8241,7 +8241,7 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>8</v>
@@ -8250,7 +8250,7 @@
         <v>2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>87.7</v>
+        <v>88</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
@@ -8264,25 +8264,25 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -8296,25 +8296,25 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>87.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -8497,52 +8497,52 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G35" s="5" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Kátia Cilene Silveira Machado</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G36" s="5" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="43" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="43" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="C36" s="43" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D36" s="43" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" s="43" t="n">
-        <v>8</v>
-      </c>
-      <c r="F36" s="43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="43" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="H36" s="43" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -8552,25 +8552,25 @@
       </c>
       <c r="B37" s="43" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C37" s="43" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D37" s="43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E37" s="43" t="n">
         <v>8</v>
       </c>
       <c r="F37" s="43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G37" s="43" t="n">
-        <v>72.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="H37" s="43" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="B38" s="43" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C38" s="43" t="inlineStr">
@@ -8599,10 +8599,10 @@
         <v>8</v>
       </c>
       <c r="F38" s="43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" s="43" t="n">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="H38" s="43" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         </is>
       </c>
       <c r="D239" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E239" s="45" t="n">
         <v>1</v>
@@ -14987,7 +14987,7 @@
         <v>1</v>
       </c>
       <c r="H239" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -15103,7 +15103,7 @@
         </is>
       </c>
       <c r="D243" s="46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E243" s="46" t="n">
         <v>1.5</v>
@@ -15115,7 +15115,7 @@
         <v>3</v>
       </c>
       <c r="H243" s="46" t="n">
-        <v>-15</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="244">
@@ -15743,7 +15743,7 @@
         </is>
       </c>
       <c r="D263" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E263" s="45" t="n">
         <v>1</v>
@@ -15755,7 +15755,7 @@
         <v>1</v>
       </c>
       <c r="H263" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="264">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="C264" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D264" s="46" t="n">
@@ -15803,23 +15803,23 @@
       </c>
       <c r="C265" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D265" s="46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E265" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F265" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G265" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H265" s="46" t="n">
-        <v>-12</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="266">
@@ -15835,87 +15835,87 @@
       </c>
       <c r="C266" s="46" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D266" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E266" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F266" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G266" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H266" s="46" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="46" t="inlineStr">
+        <is>
+          <t>Teonilda Florentino Vieira</t>
+        </is>
+      </c>
+      <c r="B267" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C267" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D266" s="46" t="n">
+      <c r="D267" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E266" s="46" t="n">
+      <c r="E267" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F266" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G266" s="46" t="n">
+      <c r="F267" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G267" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H266" s="46" t="n">
+      <c r="H267" s="46" t="n">
         <v>-1.2</v>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="45" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="45" t="inlineStr">
         <is>
           <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
-      <c r="B267" s="45" t="inlineStr">
+      <c r="B268" s="45" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C267" s="45" t="inlineStr">
+      <c r="C268" s="45" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D267" s="45" t="n">
+      <c r="D268" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E267" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F267" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G267" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H267" s="45" t="n">
+      <c r="E268" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F268" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G268" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H268" s="45" t="n">
         <v>3</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="46" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B268" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C268" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D268" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E268" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F268" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G268" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H268" s="46" t="n">
-        <v>-0.5</v>
       </c>
     </row>
     <row r="269">
@@ -15931,23 +15931,23 @@
       </c>
       <c r="C269" s="46" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D269" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E269" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F269" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G269" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H269" s="46" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="270">
@@ -15963,11 +15963,11 @@
       </c>
       <c r="C270" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D270" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E270" s="46" t="n">
         <v>0.3</v>
@@ -15979,7 +15979,7 @@
         <v>0.6</v>
       </c>
       <c r="H270" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="271">
@@ -15995,11 +15995,11 @@
       </c>
       <c r="C271" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D271" s="46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E271" s="46" t="n">
         <v>0.3</v>
@@ -16011,7 +16011,7 @@
         <v>0.6</v>
       </c>
       <c r="H271" s="46" t="n">
-        <v>-1.8</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="272">
@@ -16027,23 +16027,23 @@
       </c>
       <c r="C272" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D272" s="46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E272" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F272" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G272" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H272" s="46" t="n">
-        <v>-6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="273">
@@ -16059,87 +16059,87 @@
       </c>
       <c r="C273" s="46" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D273" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E273" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F273" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G273" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H273" s="46" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="46" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B274" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C274" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D273" s="46" t="n">
+      <c r="D274" s="46" t="n">
         <v>13</v>
       </c>
-      <c r="E273" s="46" t="n">
+      <c r="E274" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F273" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G273" s="46" t="n">
+      <c r="F274" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G274" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H273" s="46" t="n">
+      <c r="H274" s="46" t="n">
         <v>-5.2</v>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="45" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="45" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B274" s="45" t="inlineStr">
+      <c r="B275" s="45" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C274" s="45" t="inlineStr">
+      <c r="C275" s="45" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D274" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E274" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F274" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G274" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H274" s="45" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="46" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B275" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C275" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D275" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E275" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F275" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G275" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H275" s="46" t="n">
-        <v>-1</v>
+      <c r="D275" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E275" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F275" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G275" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H275" s="45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -16155,23 +16155,23 @@
       </c>
       <c r="C276" s="46" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D276" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E276" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F276" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G276" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H276" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="277">
@@ -16187,7 +16187,7 @@
       </c>
       <c r="C277" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D277" s="46" t="n">
@@ -16219,11 +16219,11 @@
       </c>
       <c r="C278" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D278" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E278" s="46" t="n">
         <v>0.3</v>
@@ -16235,7 +16235,7 @@
         <v>0.6</v>
       </c>
       <c r="H278" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="279">
@@ -16251,23 +16251,23 @@
       </c>
       <c r="C279" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D279" s="46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E279" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F279" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G279" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H279" s="46" t="n">
-        <v>-9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="280">
@@ -16283,87 +16283,87 @@
       </c>
       <c r="C280" s="46" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D280" s="46" t="n">
         <v>3</v>
       </c>
       <c r="E280" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F280" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G280" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H280" s="46" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="46" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B281" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C281" s="46" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D281" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E281" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F280" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G280" s="46" t="n">
+      <c r="F281" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G281" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H280" s="46" t="n">
+      <c r="H281" s="46" t="n">
         <v>-1.2</v>
       </c>
     </row>
-    <row r="281">
-      <c r="A281" s="45" t="inlineStr">
+    <row r="282">
+      <c r="A282" s="45" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B281" s="45" t="inlineStr">
+      <c r="B282" s="45" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C281" s="45" t="inlineStr">
+      <c r="C282" s="45" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D281" s="45" t="n">
+      <c r="D282" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="E281" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F281" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G281" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H281" s="45" t="n">
+      <c r="E282" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F282" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G282" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H282" s="45" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="46" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B282" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C282" s="46" t="inlineStr">
-        <is>
-          <t>Fim tarde antes de 16h00</t>
-        </is>
-      </c>
-      <c r="D282" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E282" s="46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F282" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G282" s="46" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H282" s="46" t="n">
-        <v>-0.6</v>
       </c>
     </row>
     <row r="283">
@@ -16379,11 +16379,11 @@
       </c>
       <c r="C283" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D283" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E283" s="46" t="n">
         <v>0.3</v>
@@ -16395,7 +16395,7 @@
         <v>0.6</v>
       </c>
       <c r="H283" s="46" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="284">
@@ -16411,11 +16411,11 @@
       </c>
       <c r="C284" s="46" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D284" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E284" s="46" t="n">
         <v>0.3</v>
@@ -16427,7 +16427,7 @@
         <v>0.6</v>
       </c>
       <c r="H284" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="285">
@@ -16443,23 +16443,23 @@
       </c>
       <c r="C285" s="46" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D285" s="46" t="n">
         <v>1</v>
       </c>
       <c r="E285" s="46" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F285" s="46" t="n">
         <v>2</v>
       </c>
       <c r="G285" s="46" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H285" s="46" t="n">
-        <v>-3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="286">
@@ -16475,55 +16475,55 @@
       </c>
       <c r="C286" s="46" t="inlineStr">
         <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D286" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E286" s="46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F286" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G286" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="H286" s="46" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="46" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B287" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C287" s="46" t="inlineStr">
+        <is>
           <t>Visita rápida</t>
         </is>
       </c>
-      <c r="D286" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E286" s="46" t="n">
+      <c r="D287" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E287" s="46" t="n">
         <v>0.2</v>
       </c>
-      <c r="F286" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G286" s="46" t="n">
+      <c r="F287" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G287" s="46" t="n">
         <v>0.4</v>
       </c>
-      <c r="H286" s="46" t="n">
+      <c r="H287" s="46" t="n">
         <v>-0.4</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="45" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B287" s="45" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C287" s="45" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D287" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E287" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="F287" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G287" s="45" t="n">
-        <v>5</v>
-      </c>
-      <c r="H287" s="45" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="288">
@@ -16539,55 +16539,55 @@
       </c>
       <c r="C288" s="45" t="inlineStr">
         <is>
+          <t>Bônus: nenhuma visita rápida no período</t>
+        </is>
+      </c>
+      <c r="D288" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E288" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F288" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G288" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="H288" s="45" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="45" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B289" s="45" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C289" s="45" t="inlineStr">
+        <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D288" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E288" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F288" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G288" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H288" s="45" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="46" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B289" s="46" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C289" s="46" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D289" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E289" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F289" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G289" s="46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H289" s="46" t="n">
-        <v>-1</v>
+      <c r="D289" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E289" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F289" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G289" s="45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H289" s="45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="290">
@@ -16603,23 +16603,23 @@
       </c>
       <c r="C290" s="46" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D290" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E290" s="46" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F290" s="46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G290" s="46" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H290" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="291">
@@ -16635,11 +16635,11 @@
       </c>
       <c r="C291" s="46" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D291" s="46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E291" s="46" t="n">
         <v>0.3</v>
@@ -16651,7 +16651,7 @@
         <v>0.6</v>
       </c>
       <c r="H291" s="46" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="292">
@@ -16667,22 +16667,54 @@
       </c>
       <c r="C292" s="46" t="inlineStr">
         <is>
+          <t>Início manhã após 08h30</t>
+        </is>
+      </c>
+      <c r="D292" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E292" s="46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F292" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G292" s="46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H292" s="46" t="n">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="46" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B293" s="46" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C293" s="46" t="inlineStr">
+        <is>
           <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
-      <c r="D292" s="46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E292" s="46" t="n">
+      <c r="D293" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E293" s="46" t="n">
         <v>1.5</v>
       </c>
-      <c r="F292" s="46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G292" s="46" t="n">
+      <c r="F293" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G293" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="H292" s="46" t="n">
+      <c r="H293" s="46" t="n">
         <v>-3</v>
       </c>
     </row>
@@ -17802,36 +17834,36 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.9</v>
+        <v>5.12</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Q005, Q006</t>
+          <t>Q005, Q006, Q007</t>
         </is>
       </c>
       <c r="I21" s="4" t="n">
         <v>3</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>7.69</v>
+        <v>5.08</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>26.42</v>
+        <v>22.37</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -19044,36 +19076,36 @@
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>6.16</v>
+        <v>6.59</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Q008, Q018, Q019, Q024</t>
+          <t>Q008, Q018, Q019, Q022, Q023, Q024, Q025, Q026</t>
         </is>
       </c>
       <c r="I44" s="5" t="n">
         <v>8</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>17.78</v>
+        <v>11.59</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>13.46</v>
+        <v>10.39</v>
       </c>
       <c r="N44" s="5" t="inlineStr">
         <is>
@@ -20048,7 +20080,7 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>17349010</t>
+          <t>17349009</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -20068,7 +20100,7 @@
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>04 - TB</t>
+          <t>03 - OU</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -20078,7 +20110,7 @@
       </c>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t>08/09/2026 16:00</t>
+          <t>08/09/2026 15:56</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr"/>
@@ -20099,7 +20131,7 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>17349009</t>
+          <t>17349010</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -20119,7 +20151,7 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t>03 - OU</t>
+          <t>04 - TB</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -20129,7 +20161,7 @@
       </c>
       <c r="J14" s="21" t="inlineStr">
         <is>
-          <t>08/09/2026 15:56</t>
+          <t>08/09/2026 16:00</t>
         </is>
       </c>
       <c r="K14" s="21" t="n">
@@ -23106,7 +23138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23121,7 +23153,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (61 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (58 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -23905,11 +23937,11 @@
     </row>
     <row r="24">
       <c r="A24" s="34" t="n">
-        <v>3035</v>
+        <v>2030</v>
       </c>
       <c r="B24" s="34" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C24" s="34" t="inlineStr">
@@ -23929,7 +23961,7 @@
       </c>
       <c r="F24" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G24" s="34" t="inlineStr">
@@ -23940,31 +23972,31 @@
     </row>
     <row r="25">
       <c r="A25" s="34" t="n">
-        <v>2030</v>
+        <v>1938</v>
       </c>
       <c r="B25" s="34" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F25" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G25" s="34" t="inlineStr">
@@ -23975,31 +24007,31 @@
     </row>
     <row r="26">
       <c r="A26" s="34" t="n">
-        <v>3035</v>
+        <v>1938</v>
       </c>
       <c r="B26" s="34" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C26" s="34" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D26" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F26" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G26" s="34" t="inlineStr">
@@ -24024,17 +24056,17 @@
       </c>
       <c r="D27" s="34" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F27" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G27" s="34" t="inlineStr">
@@ -24045,11 +24077,11 @@
     </row>
     <row r="28">
       <c r="A28" s="34" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B28" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C28" s="34" t="inlineStr">
@@ -24069,7 +24101,7 @@
       </c>
       <c r="F28" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G28" s="34" t="inlineStr">
@@ -24080,11 +24112,11 @@
     </row>
     <row r="29">
       <c r="A29" s="34" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B29" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C29" s="34" t="inlineStr">
@@ -24094,17 +24126,17 @@
       </c>
       <c r="D29" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F29" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G29" s="34" t="inlineStr">
@@ -24115,11 +24147,11 @@
     </row>
     <row r="30">
       <c r="A30" s="34" t="n">
-        <v>3038</v>
+        <v>120</v>
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C30" s="34" t="inlineStr">
@@ -24129,17 +24161,17 @@
       </c>
       <c r="D30" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E30" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F30" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G30" s="34" t="inlineStr">
@@ -24150,11 +24182,11 @@
     </row>
     <row r="31">
       <c r="A31" s="34" t="n">
-        <v>2918</v>
+        <v>1936</v>
       </c>
       <c r="B31" s="34" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
@@ -24185,11 +24217,11 @@
     </row>
     <row r="32">
       <c r="A32" s="34" t="n">
-        <v>120</v>
+        <v>1938</v>
       </c>
       <c r="B32" s="34" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C32" s="34" t="inlineStr">
@@ -24220,11 +24252,11 @@
     </row>
     <row r="33">
       <c r="A33" s="34" t="n">
-        <v>1936</v>
+        <v>3038</v>
       </c>
       <c r="B33" s="34" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C33" s="34" t="inlineStr">
@@ -24255,11 +24287,11 @@
     </row>
     <row r="34">
       <c r="A34" s="34" t="n">
-        <v>1938</v>
+        <v>3128</v>
       </c>
       <c r="B34" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C34" s="34" t="inlineStr">
@@ -24290,11 +24322,11 @@
     </row>
     <row r="35">
       <c r="A35" s="34" t="n">
-        <v>3038</v>
+        <v>2918</v>
       </c>
       <c r="B35" s="34" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C35" s="34" t="inlineStr">
@@ -24314,7 +24346,7 @@
       </c>
       <c r="F35" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G35" s="34" t="inlineStr">
@@ -24325,11 +24357,11 @@
     </row>
     <row r="36">
       <c r="A36" s="34" t="n">
-        <v>3128</v>
+        <v>120</v>
       </c>
       <c r="B36" s="34" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C36" s="34" t="inlineStr">
@@ -24349,7 +24381,7 @@
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G36" s="34" t="inlineStr">
@@ -24360,11 +24392,11 @@
     </row>
     <row r="37">
       <c r="A37" s="34" t="n">
-        <v>2918</v>
+        <v>1938</v>
       </c>
       <c r="B37" s="34" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C37" s="34" t="inlineStr">
@@ -24395,11 +24427,11 @@
     </row>
     <row r="38">
       <c r="A38" s="34" t="n">
-        <v>120</v>
+        <v>2918</v>
       </c>
       <c r="B38" s="34" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C38" s="34" t="inlineStr">
@@ -24409,17 +24441,17 @@
       </c>
       <c r="D38" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E38" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G38" s="34" t="inlineStr">
@@ -24444,17 +24476,17 @@
       </c>
       <c r="D39" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E39" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F39" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G39" s="34" t="inlineStr">
@@ -24489,7 +24521,7 @@
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G40" s="34" t="inlineStr">
@@ -24524,7 +24556,7 @@
       </c>
       <c r="F41" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G41" s="34" t="inlineStr">
@@ -24535,31 +24567,31 @@
     </row>
     <row r="42">
       <c r="A42" s="34" t="n">
-        <v>2918</v>
+        <v>2789</v>
       </c>
       <c r="B42" s="34" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C42" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D42" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E42" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G42" s="34" t="inlineStr">
@@ -24570,31 +24602,31 @@
     </row>
     <row r="43">
       <c r="A43" s="34" t="n">
-        <v>1938</v>
+        <v>149</v>
       </c>
       <c r="B43" s="34" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C43" s="34" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D43" s="34" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F43" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G43" s="34" t="inlineStr">
@@ -24605,11 +24637,11 @@
     </row>
     <row r="44">
       <c r="A44" s="34" t="n">
-        <v>2789</v>
+        <v>1996</v>
       </c>
       <c r="B44" s="34" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C44" s="34" t="inlineStr">
@@ -24640,11 +24672,11 @@
     </row>
     <row r="45">
       <c r="A45" s="34" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="B45" s="34" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C45" s="34" t="inlineStr">
@@ -24664,7 +24696,7 @@
       </c>
       <c r="F45" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G45" s="34" t="inlineStr">
@@ -24675,11 +24707,11 @@
     </row>
     <row r="46">
       <c r="A46" s="34" t="n">
-        <v>1996</v>
+        <v>2789</v>
       </c>
       <c r="B46" s="34" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C46" s="34" t="inlineStr">
@@ -24699,7 +24731,7 @@
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G46" s="34" t="inlineStr">
@@ -24710,11 +24742,11 @@
     </row>
     <row r="47">
       <c r="A47" s="34" t="n">
-        <v>110</v>
+        <v>1996</v>
       </c>
       <c r="B47" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C47" s="34" t="inlineStr">
@@ -24745,11 +24777,11 @@
     </row>
     <row r="48">
       <c r="A48" s="34" t="n">
-        <v>2789</v>
+        <v>110</v>
       </c>
       <c r="B48" s="34" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C48" s="34" t="inlineStr">
@@ -24759,17 +24791,17 @@
       </c>
       <c r="D48" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E48" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G48" s="34" t="inlineStr">
@@ -24780,11 +24812,11 @@
     </row>
     <row r="49">
       <c r="A49" s="34" t="n">
-        <v>1996</v>
+        <v>80</v>
       </c>
       <c r="B49" s="34" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C49" s="34" t="inlineStr">
@@ -24794,17 +24826,17 @@
       </c>
       <c r="D49" s="34" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F49" s="34" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G49" s="34" t="inlineStr">
@@ -24815,11 +24847,11 @@
     </row>
     <row r="50">
       <c r="A50" s="34" t="n">
-        <v>110</v>
+        <v>2789</v>
       </c>
       <c r="B50" s="34" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C50" s="34" t="inlineStr">
@@ -24850,11 +24882,11 @@
     </row>
     <row r="51">
       <c r="A51" s="34" t="n">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="B51" s="34" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C51" s="34" t="inlineStr">
@@ -24885,11 +24917,11 @@
     </row>
     <row r="52">
       <c r="A52" s="34" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B52" s="34" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C52" s="34" t="inlineStr">
@@ -24920,11 +24952,11 @@
     </row>
     <row r="53">
       <c r="A53" s="34" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B53" s="34" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C53" s="34" t="inlineStr">
@@ -24955,11 +24987,11 @@
     </row>
     <row r="54">
       <c r="A54" s="34" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B54" s="34" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
@@ -24990,11 +25022,11 @@
     </row>
     <row r="55">
       <c r="A55" s="34" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B55" s="34" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
@@ -25025,11 +25057,11 @@
     </row>
     <row r="56">
       <c r="A56" s="34" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B56" s="34" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C56" s="34" t="inlineStr">
@@ -25060,11 +25092,11 @@
     </row>
     <row r="57">
       <c r="A57" s="34" t="n">
-        <v>86</v>
+        <v>2789</v>
       </c>
       <c r="B57" s="34" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
@@ -25084,7 +25116,7 @@
       </c>
       <c r="F57" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G57" s="34" t="inlineStr">
@@ -25109,12 +25141,12 @@
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E58" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F58" s="34" t="inlineStr">
@@ -25130,11 +25162,11 @@
     </row>
     <row r="59">
       <c r="A59" s="34" t="n">
-        <v>2789</v>
+        <v>1996</v>
       </c>
       <c r="B59" s="34" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C59" s="34" t="inlineStr">
@@ -25144,12 +25176,12 @@
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F59" s="34" t="inlineStr">
@@ -25165,11 +25197,11 @@
     </row>
     <row r="60">
       <c r="A60" s="34" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B60" s="34" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C60" s="34" t="inlineStr">
@@ -25189,7 +25221,7 @@
       </c>
       <c r="F60" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G60" s="34" t="inlineStr">
@@ -25198,113 +25230,8 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="34" t="n">
-        <v>157</v>
-      </c>
-      <c r="B61" s="34" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C61" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D61" s="34" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E61" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F61" s="34" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G61" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="34" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B62" s="34" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C62" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D62" s="34" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E62" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F62" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G62" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="34" t="n">
-        <v>157</v>
-      </c>
-      <c r="B63" s="34" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C63" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D63" s="34" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E63" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F63" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G63" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G63"/>
+  <autoFilter ref="A2:G60"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semana_323.xlsx
+++ b/data/historico/semana_323.xlsx
@@ -30,8 +30,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 20min'!$A$2:$J$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Ranking'!$A$2:$H$41</definedName>
   </definedNames>
@@ -4977,25 +4977,25 @@
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>14</v>
+        <v>16.25</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>4.55</v>
+        <v>4.66</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>4</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>7.14</v>
+        <v>6.15</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>0</v>
@@ -5004,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0</v>
@@ -5019,49 +5019,49 @@
         <v>0</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>27.59</v>
+        <v>32.99</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>4.15</v>
+        <v>4.23</v>
       </c>
       <c r="W41" s="4" t="n">
-        <v>12.45</v>
+        <v>16.93</v>
       </c>
       <c r="X41" s="4" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="Y41" s="4" t="inlineStr">
         <is>
-          <t>R$ 208,32</t>
+          <t>R$ 175,09</t>
         </is>
       </c>
       <c r="Z41" s="4" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA41" s="4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AB41" s="4" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC41" s="4" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:35</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5206,7 +5206,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (3 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
+          <t>CRONOGRAMA — CHUVA/FOLGA/ATESTADO/REUNIÃO/FÉRIAS (4 registros) — EXCLUÍDOS DA ABA 'AUSÊNCIAS'. Edite em data/cronograma_ausencias.json (use cronograma_editor.html).</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B3" s="36" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>15/09/2026</t>
         </is>
       </c>
       <c r="C3" s="36" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="B4" s="36" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
       <c r="C4" s="36" t="inlineStr">
@@ -5282,27 +5282,49 @@
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Férias/Atestado (automático)</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Miglidiane Maciel Ajala</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="36" t="inlineStr">
+        <is>
           <t>06/09/2026</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>08/09/2026</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C6" s="36" t="inlineStr">
         <is>
           <t>Férias/Atestado (automático)</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D6" s="36" t="inlineStr">
         <is>
           <t>Ramona dos Santos Oliveira</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:D5"/>
+  <autoFilter ref="A2:D6"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -6498,19 +6520,19 @@
         </is>
       </c>
       <c r="C41" s="25" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D41" s="25" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E41" s="25" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="25" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="G41" s="25" t="n">
-        <v>27.59</v>
+        <v>32.99</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -6527,19 +6549,19 @@
         </is>
       </c>
       <c r="C42" s="37" t="n">
-        <v>3490</v>
+        <v>3513</v>
       </c>
       <c r="D42" s="37" t="n">
-        <v>1307</v>
+        <v>1323</v>
       </c>
       <c r="E42" s="37" t="n">
         <v>6</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>4803</v>
+        <v>4842</v>
       </c>
       <c r="G42" s="37" t="n">
-        <v>27.34</v>
+        <v>27.45</v>
       </c>
       <c r="H42" s="2" t="n"/>
       <c r="I42" s="2" t="n"/>
@@ -8072,25 +8094,25 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="4" t="n">
         <v>8</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>93</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -8104,25 +8126,25 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>92.8</v>
+        <v>93</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -8136,25 +8158,25 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>91.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
@@ -8168,12 +8190,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Evelyn Santana Santos Oliveira</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D25" s="4" t="n">
@@ -8186,43 +8208,43 @@
         <v>1</v>
       </c>
       <c r="G25" s="4" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>🟢 EXCELENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Evelyn Santana Santos Oliveira</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>🟢 EXCELENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Juliana Patricia Goncalves</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>🟡 BOM</t>
         </is>
       </c>
     </row>
@@ -8232,25 +8254,25 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>88</v>
+        <v>89.8</v>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
@@ -8264,7 +8286,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -8273,7 +8295,7 @@
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>8</v>
@@ -8282,7 +8304,7 @@
         <v>2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>87.7</v>
+        <v>88</v>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
@@ -8296,25 +8318,25 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>87.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
@@ -16127,7 +16149,7 @@
         </is>
       </c>
       <c r="D275" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E275" s="45" t="n">
         <v>1</v>
@@ -16139,7 +16161,7 @@
         <v>1</v>
       </c>
       <c r="H275" s="45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
@@ -16223,7 +16245,7 @@
         </is>
       </c>
       <c r="D278" s="46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E278" s="46" t="n">
         <v>0.3</v>
@@ -16235,7 +16257,7 @@
         <v>0.6</v>
       </c>
       <c r="H278" s="46" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="279">
@@ -16287,7 +16309,7 @@
         </is>
       </c>
       <c r="D280" s="46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E280" s="46" t="n">
         <v>1.5</v>
@@ -16299,7 +16321,7 @@
         <v>3</v>
       </c>
       <c r="H280" s="46" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="281">
@@ -16319,7 +16341,7 @@
         </is>
       </c>
       <c r="D281" s="46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E281" s="46" t="n">
         <v>0.2</v>
@@ -16331,7 +16353,7 @@
         <v>0.4</v>
       </c>
       <c r="H281" s="46" t="n">
-        <v>-1.2</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="282">
@@ -19184,36 +19206,36 @@
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>4.55</v>
+        <v>4.66</v>
       </c>
       <c r="F46" s="4" t="n">
         <v>4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Q007, Q011, Q012, Q013, Q014</t>
+          <t>Q007, Q011, Q012, Q013, Q014, Q016, Q017</t>
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>7.14</v>
+        <v>6.15</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="L46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>27.59</v>
+        <v>32.99</v>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
@@ -23138,7 +23160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -23153,7 +23175,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (58 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (56 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -25127,11 +25149,11 @@
     </row>
     <row r="58">
       <c r="A58" s="34" t="n">
-        <v>157</v>
+        <v>1996</v>
       </c>
       <c r="B58" s="34" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C58" s="34" t="inlineStr">
@@ -25151,7 +25173,7 @@
       </c>
       <c r="F58" s="34" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G58" s="34" t="inlineStr">
@@ -25160,78 +25182,8 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="34" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B59" s="34" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C59" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D59" s="34" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E59" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F59" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G59" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="34" t="n">
-        <v>157</v>
-      </c>
-      <c r="B60" s="34" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C60" s="34" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D60" s="34" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E60" s="34" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F60" s="34" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G60" s="34" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G60"/>
+  <autoFilter ref="A2:G58"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
